--- a/Master/Master_DATA.xlsx
+++ b/Master/Master_DATA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -781,6 +781,9 @@
     <t>2025-02-20</t>
   </si>
   <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
     <t>2025-02-24</t>
   </si>
   <si>
@@ -916,12 +919,6 @@
     <t>2025-04-25</t>
   </si>
   <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
     <t>2025-04-28</t>
   </si>
   <si>
@@ -1063,6 +1060,9 @@
     <t>2025-06-27</t>
   </si>
   <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
     <t>2025-07-01</t>
   </si>
   <si>
@@ -1514,6 +1514,453 @@
   </si>
   <si>
     <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>2026-02-06</t>
+  </si>
+  <si>
+    <t>2026-02-09</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-02-11</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
   </si>
   <si>
     <t>VANGUARDDD.INTERMEDIATETERMCORPORATEBONDETF.AVGDURATION.B</t>
@@ -1538,9 +1985,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -1570,9 +2014,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1867,7 +2310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D650"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1875,24 +2318,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>500</v>
+        <v>649</v>
       </c>
       <c r="C1" t="s">
-        <v>502</v>
+        <v>651</v>
       </c>
       <c r="D1" t="s">
-        <v>504</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>501</v>
+        <v>650</v>
       </c>
       <c r="C2" t="s">
-        <v>503</v>
+        <v>652</v>
       </c>
       <c r="D2" t="s">
-        <v>505</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1911,7 +2354,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>6.1</v>
@@ -1920,12 +2363,12 @@
         <v>2.6</v>
       </c>
       <c r="D4">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>6.1</v>
@@ -1939,7 +2382,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>6.1</v>
@@ -1953,7 +2396,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>6.1</v>
@@ -1967,7 +2410,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>6.1</v>
@@ -1976,12 +2419,12 @@
         <v>2.6</v>
       </c>
       <c r="D8">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>6.1</v>
@@ -1995,7 +2438,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>6.1</v>
@@ -2009,7 +2452,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>6.1</v>
@@ -2023,7 +2466,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>6.1</v>
@@ -2037,7 +2480,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>6.1</v>
@@ -2051,7 +2494,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>6.1</v>
@@ -2065,7 +2508,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>6.1</v>
@@ -2079,7 +2522,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>6.1</v>
@@ -2093,7 +2536,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>6.1</v>
@@ -2107,7 +2550,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>6.1</v>
@@ -2121,7 +2564,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>6.1</v>
@@ -2130,12 +2573,12 @@
         <v>2.6</v>
       </c>
       <c r="D19">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>6.1</v>
@@ -2149,7 +2592,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>6.1</v>
@@ -2163,7 +2606,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>6.1</v>
@@ -2177,7 +2620,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>6.1</v>
@@ -2191,7 +2634,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24">
         <v>6.1</v>
@@ -2205,7 +2648,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>6.1</v>
@@ -2219,7 +2662,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>6.1</v>
@@ -2233,7 +2676,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>6.1</v>
@@ -2247,7 +2690,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28">
         <v>6.1</v>
@@ -2261,7 +2704,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>6.1</v>
@@ -2275,7 +2718,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>6.1</v>
@@ -2289,7 +2732,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>6.1</v>
@@ -2303,7 +2746,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32">
         <v>6.1</v>
@@ -2317,7 +2760,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33">
         <v>6.1</v>
@@ -2331,7 +2774,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34">
         <v>6.1</v>
@@ -2345,7 +2788,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35">
         <v>6.1</v>
@@ -2359,7 +2802,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36">
         <v>6.1</v>
@@ -2373,7 +2816,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37">
         <v>6.1</v>
@@ -2387,7 +2830,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38">
         <v>6.1</v>
@@ -2401,7 +2844,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39">
         <v>6.1</v>
@@ -2415,7 +2858,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40">
         <v>6.1</v>
@@ -2429,7 +2872,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41">
         <v>6.1</v>
@@ -2438,12 +2881,12 @@
         <v>2.6</v>
       </c>
       <c r="D41">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42">
         <v>6.1</v>
@@ -2457,7 +2900,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43">
         <v>6.1</v>
@@ -2471,7 +2914,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44">
         <v>6.1</v>
@@ -2485,7 +2928,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45">
         <v>6.1</v>
@@ -2499,7 +2942,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46">
         <v>6.1</v>
@@ -2513,7 +2956,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47">
         <v>6.1</v>
@@ -2527,7 +2970,7 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48">
         <v>6.1</v>
@@ -2541,7 +2984,7 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49">
         <v>6.1</v>
@@ -2555,7 +2998,7 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50">
         <v>6.1</v>
@@ -2569,7 +3012,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51">
         <v>6.1</v>
@@ -2583,7 +3026,7 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52">
         <v>6.1</v>
@@ -2597,7 +3040,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53">
         <v>6.1</v>
@@ -2611,7 +3054,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54">
         <v>6.1</v>
@@ -2625,7 +3068,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55">
         <v>6.1</v>
@@ -2639,7 +3082,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56">
         <v>6.1</v>
@@ -2653,7 +3096,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57">
         <v>6.1</v>
@@ -2667,7 +3110,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B58">
         <v>6.1</v>
@@ -2681,7 +3124,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59">
         <v>6.1</v>
@@ -2695,7 +3138,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60">
         <v>6.1</v>
@@ -2709,7 +3152,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61">
         <v>6.1</v>
@@ -2723,7 +3166,7 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62">
         <v>6.1</v>
@@ -2737,7 +3180,7 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63">
         <v>6.1</v>
@@ -2751,7 +3194,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64">
         <v>6.1</v>
@@ -2765,7 +3208,7 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65">
         <v>6.1</v>
@@ -2779,7 +3222,7 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66">
         <v>6.1</v>
@@ -2793,7 +3236,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B67">
         <v>6.1</v>
@@ -2807,7 +3250,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B68">
         <v>6.1</v>
@@ -2821,7 +3264,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B69">
         <v>6.1</v>
@@ -2835,7 +3278,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B70">
         <v>6.1</v>
@@ -2849,7 +3292,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B71">
         <v>6.1</v>
@@ -2863,7 +3306,7 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72">
         <v>6.1</v>
@@ -2877,7 +3320,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B73">
         <v>6.1</v>
@@ -2891,7 +3334,7 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B74">
         <v>6.1</v>
@@ -2905,7 +3348,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B75">
         <v>6.1</v>
@@ -2919,7 +3362,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B76">
         <v>6.1</v>
@@ -2933,7 +3376,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B77">
         <v>6.1</v>
@@ -2947,7 +3390,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B78">
         <v>6.1</v>
@@ -2961,7 +3404,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B79">
         <v>6.1</v>
@@ -2975,7 +3418,7 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B80">
         <v>6.1</v>
@@ -2989,7 +3432,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B81">
         <v>6.1</v>
@@ -3003,7 +3446,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82">
         <v>6.1</v>
@@ -3017,7 +3460,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B83">
         <v>6.1</v>
@@ -3031,7 +3474,7 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B84">
         <v>6.1</v>
@@ -3045,7 +3488,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B85">
         <v>6.1</v>
@@ -3059,7 +3502,7 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B86">
         <v>6.1</v>
@@ -3073,7 +3516,7 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B87">
         <v>6.1</v>
@@ -3087,7 +3530,7 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88">
         <v>6.1</v>
@@ -3101,7 +3544,7 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B89">
         <v>6.1</v>
@@ -3115,7 +3558,7 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B90">
         <v>6.1</v>
@@ -3129,7 +3572,7 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91">
         <v>6.1</v>
@@ -3143,7 +3586,7 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B92">
         <v>6.1</v>
@@ -3157,7 +3600,7 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B93">
         <v>6.1</v>
@@ -3171,7 +3614,7 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B94">
         <v>6.1</v>
@@ -3185,7 +3628,7 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B95">
         <v>6.1</v>
@@ -3199,7 +3642,7 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B96">
         <v>6.1</v>
@@ -3213,7 +3656,7 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B97">
         <v>6.1</v>
@@ -3227,7 +3670,7 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B98">
         <v>6.1</v>
@@ -3241,7 +3684,7 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B99">
         <v>6.1</v>
@@ -3255,7 +3698,7 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B100">
         <v>6.1</v>
@@ -3269,7 +3712,7 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B101">
         <v>6.1</v>
@@ -3283,7 +3726,7 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B102">
         <v>6.1</v>
@@ -3297,7 +3740,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B103">
         <v>6.1</v>
@@ -3311,7 +3754,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B104">
         <v>6.1</v>
@@ -3325,7 +3768,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B105">
         <v>6.1</v>
@@ -3339,7 +3782,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B106">
         <v>6.1</v>
@@ -3353,7 +3796,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B107">
         <v>6.1</v>
@@ -3367,7 +3810,7 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B108">
         <v>6.1</v>
@@ -3376,12 +3819,12 @@
         <v>2.6</v>
       </c>
       <c r="D108">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B109">
         <v>6.1</v>
@@ -3395,7 +3838,7 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B110">
         <v>6.1</v>
@@ -3409,7 +3852,7 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B111">
         <v>6.1</v>
@@ -3423,7 +3866,7 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B112">
         <v>6.1</v>
@@ -3437,7 +3880,7 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B113">
         <v>6.1</v>
@@ -3451,7 +3894,7 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B114">
         <v>6.1</v>
@@ -3465,7 +3908,7 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B115">
         <v>6.1</v>
@@ -3479,7 +3922,7 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B116">
         <v>6.1</v>
@@ -3493,7 +3936,7 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B117">
         <v>6.1</v>
@@ -3507,7 +3950,7 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B118">
         <v>6.1</v>
@@ -3521,7 +3964,7 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B119">
         <v>6.1</v>
@@ -3535,7 +3978,7 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B120">
         <v>6.1</v>
@@ -3549,7 +3992,7 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B121">
         <v>6.1</v>
@@ -3563,7 +4006,7 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B122">
         <v>6.1</v>
@@ -3577,7 +4020,7 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B123">
         <v>6.1</v>
@@ -3591,7 +4034,7 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B124">
         <v>6.1</v>
@@ -3605,7 +4048,7 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B125">
         <v>6.1</v>
@@ -3619,7 +4062,7 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B126">
         <v>6.1</v>
@@ -3633,7 +4076,7 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B127">
         <v>6.1</v>
@@ -3647,7 +4090,7 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B128">
         <v>6.1</v>
@@ -3661,7 +4104,7 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B129">
         <v>6.1</v>
@@ -3675,7 +4118,7 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B130">
         <v>6.1</v>
@@ -3684,12 +4127,12 @@
         <v>2.6</v>
       </c>
       <c r="D130">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B131">
         <v>6.1</v>
@@ -3703,7 +4146,7 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B132">
         <v>6.1</v>
@@ -3717,7 +4160,7 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B133">
         <v>6.1</v>
@@ -3731,7 +4174,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B134">
         <v>6.1</v>
@@ -3745,7 +4188,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B135">
         <v>6.1</v>
@@ -3759,7 +4202,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B136">
         <v>6.1</v>
@@ -3773,7 +4216,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B137">
         <v>6.1</v>
@@ -3787,7 +4230,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B138">
         <v>6.1</v>
@@ -3801,7 +4244,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B139">
         <v>6.1</v>
@@ -3815,7 +4258,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B140">
         <v>6.1</v>
@@ -3829,7 +4272,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B141">
         <v>6.1</v>
@@ -3843,7 +4286,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B142">
         <v>6.1</v>
@@ -3857,7 +4300,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B143">
         <v>6.1</v>
@@ -3871,7 +4314,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B144">
         <v>6.1</v>
@@ -3885,7 +4328,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B145">
         <v>6.1</v>
@@ -3899,7 +4342,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B146">
         <v>6.1</v>
@@ -3913,7 +4356,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B147">
         <v>6.1</v>
@@ -3927,7 +4370,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B148">
         <v>6.1</v>
@@ -3941,7 +4384,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B149">
         <v>6.1</v>
@@ -3955,7 +4398,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B150">
         <v>6.1</v>
@@ -3969,7 +4412,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B151">
         <v>6.1</v>
@@ -3983,7 +4426,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B152">
         <v>6.1</v>
@@ -3997,7 +4440,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B153">
         <v>6.1</v>
@@ -4006,12 +4449,12 @@
         <v>2.6</v>
       </c>
       <c r="D153">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B154">
         <v>6.1</v>
@@ -4025,7 +4468,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B155">
         <v>6.1</v>
@@ -4039,7 +4482,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B156">
         <v>6.1</v>
@@ -4053,7 +4496,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B157">
         <v>6.1</v>
@@ -4067,7 +4510,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B158">
         <v>6.1</v>
@@ -4081,7 +4524,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B159">
         <v>6.1</v>
@@ -4095,7 +4538,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B160">
         <v>6.1</v>
@@ -4109,7 +4552,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B161">
         <v>6.1</v>
@@ -4123,7 +4566,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B162">
         <v>6.1</v>
@@ -4137,7 +4580,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B163">
         <v>6.1</v>
@@ -4151,7 +4594,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B164">
         <v>6.1</v>
@@ -4165,7 +4608,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B165">
         <v>6.1</v>
@@ -4179,7 +4622,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B166">
         <v>6.1</v>
@@ -4193,7 +4636,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B167">
         <v>6.1</v>
@@ -4207,7 +4650,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B168">
         <v>6.1</v>
@@ -4221,7 +4664,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B169">
         <v>6.1</v>
@@ -4235,7 +4678,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B170">
         <v>6.1</v>
@@ -4249,7 +4692,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B171">
         <v>6.1</v>
@@ -4263,7 +4706,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B172">
         <v>6.1</v>
@@ -4277,7 +4720,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B173">
         <v>6.1</v>
@@ -4291,7 +4734,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B174">
         <v>6.1</v>
@@ -4305,7 +4748,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B175">
         <v>6.1</v>
@@ -4319,21 +4762,21 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B176">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="C176">
         <v>2.6</v>
       </c>
       <c r="D176">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B177">
         <v>6</v>
@@ -4347,7 +4790,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B178">
         <v>6</v>
@@ -4361,7 +4804,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B179">
         <v>6</v>
@@ -4375,7 +4818,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B180">
         <v>6</v>
@@ -4389,7 +4832,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B181">
         <v>6</v>
@@ -4403,7 +4846,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B182">
         <v>6</v>
@@ -4417,7 +4860,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B183">
         <v>6</v>
@@ -4431,7 +4874,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B184">
         <v>6</v>
@@ -4445,7 +4888,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B185">
         <v>6</v>
@@ -4459,7 +4902,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B186">
         <v>6</v>
@@ -4473,7 +4916,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B187">
         <v>6</v>
@@ -4487,7 +4930,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B188">
         <v>6</v>
@@ -4501,7 +4944,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B189">
         <v>6</v>
@@ -4515,7 +4958,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B190">
         <v>6</v>
@@ -4529,7 +4972,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B191">
         <v>6</v>
@@ -4543,7 +4986,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B192">
         <v>6</v>
@@ -4557,7 +5000,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B193">
         <v>6</v>
@@ -4571,7 +5014,7 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B194">
         <v>6</v>
@@ -4585,7 +5028,7 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B195">
         <v>6</v>
@@ -4599,7 +5042,7 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B196">
         <v>6</v>
@@ -4613,7 +5056,7 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B197">
         <v>6</v>
@@ -4627,7 +5070,7 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B198">
         <v>6</v>
@@ -4636,12 +5079,12 @@
         <v>2.6</v>
       </c>
       <c r="D198">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B199">
         <v>6</v>
@@ -4655,7 +5098,7 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B200">
         <v>6</v>
@@ -4669,7 +5112,7 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B201">
         <v>6</v>
@@ -4683,7 +5126,7 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B202">
         <v>6</v>
@@ -4697,7 +5140,7 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B203">
         <v>6</v>
@@ -4711,7 +5154,7 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B204">
         <v>6</v>
@@ -4725,7 +5168,7 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B205">
         <v>6</v>
@@ -4739,7 +5182,7 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B206">
         <v>6</v>
@@ -4753,7 +5196,7 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B207">
         <v>6</v>
@@ -4767,7 +5210,7 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B208">
         <v>6</v>
@@ -4781,7 +5224,7 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B209">
         <v>6</v>
@@ -4795,7 +5238,7 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B210">
         <v>6</v>
@@ -4809,7 +5252,7 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B211">
         <v>6</v>
@@ -4823,7 +5266,7 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B212">
         <v>6</v>
@@ -4837,7 +5280,7 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B213">
         <v>6</v>
@@ -4851,7 +5294,7 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B214">
         <v>6</v>
@@ -4865,7 +5308,7 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B215">
         <v>6</v>
@@ -4879,7 +5322,7 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B216">
         <v>6</v>
@@ -4893,7 +5336,7 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B217">
         <v>6</v>
@@ -4907,7 +5350,7 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B218">
         <v>6</v>
@@ -4921,21 +5364,21 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B219">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="C219">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D219">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B220">
         <v>5.9</v>
@@ -4949,7 +5392,7 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B221">
         <v>5.9</v>
@@ -4963,7 +5406,7 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B222">
         <v>5.9</v>
@@ -4977,7 +5420,7 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B223">
         <v>5.9</v>
@@ -4991,7 +5434,7 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B224">
         <v>5.9</v>
@@ -5005,7 +5448,7 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B225">
         <v>5.9</v>
@@ -5019,7 +5462,7 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B226">
         <v>5.9</v>
@@ -5033,7 +5476,7 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B227">
         <v>5.9</v>
@@ -5047,7 +5490,7 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B228">
         <v>5.9</v>
@@ -5061,7 +5504,7 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B229">
         <v>5.9</v>
@@ -5075,7 +5518,7 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B230">
         <v>5.9</v>
@@ -5089,7 +5532,7 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B231">
         <v>5.9</v>
@@ -5103,7 +5546,7 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B232">
         <v>5.9</v>
@@ -5117,7 +5560,7 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B233">
         <v>5.9</v>
@@ -5131,7 +5574,7 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B234">
         <v>5.9</v>
@@ -5145,7 +5588,7 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B235">
         <v>5.9</v>
@@ -5159,7 +5602,7 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B236">
         <v>5.9</v>
@@ -5173,7 +5616,7 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B237">
         <v>5.9</v>
@@ -5187,7 +5630,7 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B238">
         <v>5.9</v>
@@ -5201,7 +5644,7 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B239">
         <v>5.9</v>
@@ -5215,7 +5658,7 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B240">
         <v>5.9</v>
@@ -5229,7 +5672,7 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B241">
         <v>5.9</v>
@@ -5243,21 +5686,21 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B242">
         <v>5.9</v>
       </c>
       <c r="C242">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="D242">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B243">
         <v>5.9</v>
@@ -5271,7 +5714,7 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B244">
         <v>5.9</v>
@@ -5285,7 +5728,7 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B245">
         <v>5.9</v>
@@ -5299,7 +5742,7 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B246">
         <v>5.9</v>
@@ -5313,7 +5756,7 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B247">
         <v>5.9</v>
@@ -5327,7 +5770,7 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B248">
         <v>5.9</v>
@@ -5341,7 +5784,7 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B249">
         <v>5.9</v>
@@ -5355,7 +5798,7 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B250">
         <v>5.9</v>
@@ -5369,7 +5812,7 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B251">
         <v>5.9</v>
@@ -5383,7 +5826,7 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B252">
         <v>5.9</v>
@@ -5397,7 +5840,7 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B253">
         <v>5.9</v>
@@ -5411,7 +5854,7 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B254">
         <v>5.9</v>
@@ -5425,7 +5868,7 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B255">
         <v>5.9</v>
@@ -5439,7 +5882,7 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B256">
         <v>5.9</v>
@@ -5453,7 +5896,7 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B257">
         <v>5.9</v>
@@ -5467,7 +5910,7 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B258">
         <v>5.9</v>
@@ -5481,7 +5924,7 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B259">
         <v>5.9</v>
@@ -5495,7 +5938,7 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B260">
         <v>5.9</v>
@@ -5509,7 +5952,7 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B261">
         <v>5.9</v>
@@ -5523,7 +5966,7 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B262">
         <v>6</v>
@@ -5537,7 +5980,7 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B263">
         <v>6</v>
@@ -5551,7 +5994,7 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B264">
         <v>6</v>
@@ -5565,7 +6008,7 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B265">
         <v>6</v>
@@ -5579,7 +6022,7 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B266">
         <v>6</v>
@@ -5593,7 +6036,7 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B267">
         <v>6</v>
@@ -5607,7 +6050,7 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B268">
         <v>6</v>
@@ -5621,7 +6064,7 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B269">
         <v>6</v>
@@ -5635,7 +6078,7 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B270">
         <v>6</v>
@@ -5649,7 +6092,7 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B271">
         <v>6</v>
@@ -5663,7 +6106,7 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B272">
         <v>6</v>
@@ -5677,7 +6120,7 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B273">
         <v>6</v>
@@ -5691,7 +6134,7 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B274">
         <v>6</v>
@@ -5705,7 +6148,7 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B275">
         <v>6</v>
@@ -5719,7 +6162,7 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B276">
         <v>6</v>
@@ -5733,7 +6176,7 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B277">
         <v>6</v>
@@ -5747,7 +6190,7 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B278">
         <v>6</v>
@@ -5761,7 +6204,7 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B279">
         <v>6</v>
@@ -5775,7 +6218,7 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B280">
         <v>6</v>
@@ -5789,7 +6232,7 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B281">
         <v>6</v>
@@ -5803,7 +6246,7 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B282">
         <v>6</v>
@@ -5817,7 +6260,7 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B283">
         <v>6</v>
@@ -5831,7 +6274,7 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B284">
         <v>6</v>
@@ -5845,7 +6288,7 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B285">
         <v>6</v>
@@ -5859,7 +6302,7 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B286">
         <v>6</v>
@@ -5873,7 +6316,7 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B287">
         <v>6</v>
@@ -5887,7 +6330,7 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B288">
         <v>6</v>
@@ -5901,7 +6344,7 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B289">
         <v>6</v>
@@ -5915,7 +6358,7 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B290">
         <v>6</v>
@@ -5929,7 +6372,7 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B291">
         <v>6</v>
@@ -5943,7 +6386,7 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B292">
         <v>6</v>
@@ -5957,7 +6400,7 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B293">
         <v>6</v>
@@ -5971,7 +6414,7 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B294">
         <v>6</v>
@@ -5985,7 +6428,7 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B295">
         <v>6</v>
@@ -5999,7 +6442,7 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B296">
         <v>6</v>
@@ -6013,7 +6456,7 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B297">
         <v>6</v>
@@ -6027,7 +6470,7 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B298">
         <v>6</v>
@@ -6041,7 +6484,7 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B299">
         <v>6</v>
@@ -6055,7 +6498,7 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B300">
         <v>6</v>
@@ -6069,7 +6512,7 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B301">
         <v>6</v>
@@ -6083,7 +6526,7 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B302">
         <v>6</v>
@@ -6097,7 +6540,7 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B303">
         <v>6</v>
@@ -6111,7 +6554,7 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B304">
         <v>6</v>
@@ -6125,245 +6568,245 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B305">
         <v>6</v>
       </c>
       <c r="C305">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D305">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B306">
         <v>6</v>
       </c>
       <c r="C306">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D306">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B307">
         <v>6</v>
       </c>
       <c r="C307">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D307">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B308">
         <v>6</v>
       </c>
       <c r="C308">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D308">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B309">
         <v>6</v>
       </c>
       <c r="C309">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D309">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B310">
         <v>6</v>
       </c>
       <c r="C310">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D310">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B311">
         <v>6</v>
       </c>
       <c r="C311">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D311">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B312">
         <v>6</v>
       </c>
       <c r="C312">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D312">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B313">
         <v>6</v>
       </c>
       <c r="C313">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D313">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B314">
         <v>6</v>
       </c>
       <c r="C314">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D314">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B315">
         <v>6</v>
       </c>
       <c r="C315">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D315">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B316">
         <v>6</v>
       </c>
       <c r="C316">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D316">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B317">
         <v>6</v>
       </c>
       <c r="C317">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D317">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B318">
         <v>6</v>
       </c>
       <c r="C318">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D318">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B319">
         <v>6</v>
       </c>
       <c r="C319">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D319">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B320">
         <v>6</v>
       </c>
       <c r="C320">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D320">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B321">
         <v>6</v>
       </c>
       <c r="C321">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D321">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B322">
         <v>6</v>
@@ -6377,7 +6820,7 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B323">
         <v>6</v>
@@ -6391,7 +6834,7 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B324">
         <v>6</v>
@@ -6405,7 +6848,7 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B325">
         <v>6</v>
@@ -6419,7 +6862,7 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B326">
         <v>6</v>
@@ -6433,7 +6876,7 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B327">
         <v>6</v>
@@ -6447,10 +6890,10 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B328">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="C328">
         <v>2.7</v>
@@ -6461,10 +6904,10 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B329">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="C329">
         <v>2.7</v>
@@ -6475,7 +6918,7 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B330">
         <v>6.1</v>
@@ -6489,7 +6932,7 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B331">
         <v>6.1</v>
@@ -6503,7 +6946,7 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B332">
         <v>6.1</v>
@@ -6517,7 +6960,7 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B333">
         <v>6.1</v>
@@ -6531,7 +6974,7 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B334">
         <v>6.1</v>
@@ -6545,7 +6988,7 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B335">
         <v>6.1</v>
@@ -6559,7 +7002,7 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B336">
         <v>6.1</v>
@@ -6573,7 +7016,7 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B337">
         <v>6.1</v>
@@ -6587,7 +7030,7 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B338">
         <v>6.1</v>
@@ -6601,7 +7044,7 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B339">
         <v>6.1</v>
@@ -6615,7 +7058,7 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B340">
         <v>6.1</v>
@@ -6629,7 +7072,7 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B341">
         <v>6.1</v>
@@ -6643,7 +7086,7 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B342">
         <v>6.1</v>
@@ -6657,7 +7100,7 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B343">
         <v>6.1</v>
@@ -6671,7 +7114,7 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B344">
         <v>6.1</v>
@@ -6685,7 +7128,7 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B345">
         <v>6.1</v>
@@ -6699,7 +7142,7 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B346">
         <v>6.1</v>
@@ -6713,7 +7156,7 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B347">
         <v>6.1</v>
@@ -6727,7 +7170,7 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B348">
         <v>6.1</v>
@@ -6741,7 +7184,7 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B349">
         <v>6.1</v>
@@ -6755,7 +7198,7 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B350">
         <v>6.1</v>
@@ -6769,7 +7212,7 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B351">
         <v>6.1</v>
@@ -6783,7 +7226,7 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B352">
         <v>6.1</v>
@@ -6797,7 +7240,7 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B353">
         <v>6.1</v>
@@ -6811,7 +7254,7 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B354">
         <v>6.1</v>
@@ -6825,7 +7268,7 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B355">
         <v>6.1</v>
@@ -6839,7 +7282,7 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B356">
         <v>6.1</v>
@@ -6853,7 +7296,7 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B357">
         <v>6.1</v>
@@ -6867,7 +7310,7 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B358">
         <v>6.1</v>
@@ -6881,7 +7324,7 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B359">
         <v>6.1</v>
@@ -6895,7 +7338,7 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B360">
         <v>6.1</v>
@@ -6909,7 +7352,7 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B361">
         <v>6.1</v>
@@ -6923,7 +7366,7 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B362">
         <v>6.1</v>
@@ -6937,7 +7380,7 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B363">
         <v>6.1</v>
@@ -6951,7 +7394,7 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B364">
         <v>6.1</v>
@@ -6965,7 +7408,7 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B365">
         <v>6.1</v>
@@ -6979,7 +7422,7 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B366">
         <v>6.1</v>
@@ -6993,7 +7436,7 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B367">
         <v>6.1</v>
@@ -7007,7 +7450,7 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B368">
         <v>6.1</v>
@@ -7021,7 +7464,7 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B369">
         <v>6.1</v>
@@ -7035,7 +7478,7 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B370">
         <v>6.1</v>
@@ -7049,7 +7492,7 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B371">
         <v>6.1</v>
@@ -7063,7 +7506,7 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B372">
         <v>6.1</v>
@@ -7077,7 +7520,7 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B373">
         <v>6.1</v>
@@ -7091,7 +7534,7 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B374">
         <v>6.1</v>
@@ -7105,7 +7548,7 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B375">
         <v>6.1</v>
@@ -7119,7 +7562,7 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B376">
         <v>6.1</v>
@@ -7133,7 +7576,7 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B377">
         <v>6.1</v>
@@ -7147,7 +7590,7 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B378">
         <v>6.1</v>
@@ -7161,7 +7604,7 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B379">
         <v>6.1</v>
@@ -7175,7 +7618,7 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B380">
         <v>6.1</v>
@@ -7189,7 +7632,7 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B381">
         <v>6.1</v>
@@ -7203,7 +7646,7 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B382">
         <v>6.1</v>
@@ -7217,7 +7660,7 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B383">
         <v>6.1</v>
@@ -7231,7 +7674,7 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B384">
         <v>6.1</v>
@@ -7245,7 +7688,7 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B385">
         <v>6.1</v>
@@ -7259,7 +7702,7 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B386">
         <v>6.1</v>
@@ -7273,7 +7716,7 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B387">
         <v>6.1</v>
@@ -7287,7 +7730,7 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B388">
         <v>6.1</v>
@@ -7301,7 +7744,7 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B389">
         <v>6.1</v>
@@ -7315,7 +7758,7 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B390">
         <v>6.1</v>
@@ -7329,7 +7772,7 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B391">
         <v>6.1</v>
@@ -7343,7 +7786,7 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B392">
         <v>6.1</v>
@@ -7357,7 +7800,7 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B393">
         <v>6.1</v>
@@ -7371,7 +7814,7 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B394">
         <v>6.1</v>
@@ -7385,7 +7828,7 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B395">
         <v>6.1</v>
@@ -7394,12 +7837,12 @@
         <v>2.7</v>
       </c>
       <c r="D395">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B396">
         <v>6.1</v>
@@ -7413,7 +7856,7 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B397">
         <v>6.1</v>
@@ -7427,7 +7870,7 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B398">
         <v>6.1</v>
@@ -7441,7 +7884,7 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B399">
         <v>6.1</v>
@@ -7455,7 +7898,7 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B400">
         <v>6.1</v>
@@ -7469,7 +7912,7 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B401">
         <v>6.1</v>
@@ -7483,7 +7926,7 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B402">
         <v>6.1</v>
@@ -7497,7 +7940,7 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B403">
         <v>6.1</v>
@@ -7511,7 +7954,7 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B404">
         <v>6.1</v>
@@ -7525,7 +7968,7 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B405">
         <v>6.1</v>
@@ -7539,7 +7982,7 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B406">
         <v>6.1</v>
@@ -7553,7 +7996,7 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B407">
         <v>6.1</v>
@@ -7567,7 +8010,7 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B408">
         <v>6.1</v>
@@ -7581,7 +8024,7 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B409">
         <v>6.1</v>
@@ -7595,7 +8038,7 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B410">
         <v>6.1</v>
@@ -7609,7 +8052,7 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B411">
         <v>6.1</v>
@@ -7623,7 +8066,7 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B412">
         <v>6.1</v>
@@ -7637,7 +8080,7 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B413">
         <v>6.1</v>
@@ -7651,7 +8094,7 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B414">
         <v>6.1</v>
@@ -7665,7 +8108,7 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B415">
         <v>6.1</v>
@@ -7679,7 +8122,7 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B416">
         <v>6.1</v>
@@ -7693,7 +8136,7 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B417">
         <v>6.1</v>
@@ -7702,12 +8145,12 @@
         <v>2.7</v>
       </c>
       <c r="D417">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B418">
         <v>6.1</v>
@@ -7721,7 +8164,7 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B419">
         <v>6.1</v>
@@ -7735,7 +8178,7 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B420">
         <v>6.1</v>
@@ -7749,7 +8192,7 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B421">
         <v>6.1</v>
@@ -7763,7 +8206,7 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B422">
         <v>6.1</v>
@@ -7777,7 +8220,7 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B423">
         <v>6.1</v>
@@ -7791,7 +8234,7 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B424">
         <v>6.1</v>
@@ -7805,7 +8248,7 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B425">
         <v>6.1</v>
@@ -7819,7 +8262,7 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B426">
         <v>6.1</v>
@@ -7833,7 +8276,7 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B427">
         <v>6.1</v>
@@ -7847,7 +8290,7 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B428">
         <v>6.1</v>
@@ -7861,7 +8304,7 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B429">
         <v>6.1</v>
@@ -7875,7 +8318,7 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B430">
         <v>6.1</v>
@@ -7889,7 +8332,7 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B431">
         <v>6.1</v>
@@ -7903,7 +8346,7 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B432">
         <v>6.1</v>
@@ -7917,7 +8360,7 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B433">
         <v>6.1</v>
@@ -7931,7 +8374,7 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B434">
         <v>6.1</v>
@@ -7945,7 +8388,7 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B435">
         <v>6.1</v>
@@ -7959,7 +8402,7 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B436">
         <v>6.1</v>
@@ -7973,7 +8416,7 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B437">
         <v>6.1</v>
@@ -7987,7 +8430,7 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B438">
         <v>6.1</v>
@@ -8001,7 +8444,7 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B439">
         <v>6.1</v>
@@ -8015,10 +8458,10 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B440">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="C440">
         <v>2.7</v>
@@ -8029,7 +8472,7 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B441">
         <v>6</v>
@@ -8043,7 +8486,7 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B442">
         <v>6</v>
@@ -8057,7 +8500,7 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B443">
         <v>6</v>
@@ -8071,7 +8514,7 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B444">
         <v>6</v>
@@ -8085,7 +8528,7 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B445">
         <v>6</v>
@@ -8099,7 +8542,7 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B446">
         <v>6</v>
@@ -8113,7 +8556,7 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B447">
         <v>6</v>
@@ -8127,7 +8570,7 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B448">
         <v>6</v>
@@ -8141,7 +8584,7 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B449">
         <v>6</v>
@@ -8155,7 +8598,7 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B450">
         <v>6</v>
@@ -8169,7 +8612,7 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B451">
         <v>6</v>
@@ -8183,7 +8626,7 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B452">
         <v>6</v>
@@ -8197,7 +8640,7 @@
     </row>
     <row r="453" spans="1:4">
       <c r="A453" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B453">
         <v>6</v>
@@ -8211,7 +8654,7 @@
     </row>
     <row r="454" spans="1:4">
       <c r="A454" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B454">
         <v>6</v>
@@ -8225,7 +8668,7 @@
     </row>
     <row r="455" spans="1:4">
       <c r="A455" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B455">
         <v>6</v>
@@ -8239,7 +8682,7 @@
     </row>
     <row r="456" spans="1:4">
       <c r="A456" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B456">
         <v>6</v>
@@ -8253,7 +8696,7 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B457">
         <v>6</v>
@@ -8267,7 +8710,7 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B458">
         <v>6</v>
@@ -8281,7 +8724,7 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B459">
         <v>6</v>
@@ -8295,7 +8738,7 @@
     </row>
     <row r="460" spans="1:4">
       <c r="A460" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B460">
         <v>6</v>
@@ -8309,7 +8752,7 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B461">
         <v>6</v>
@@ -8323,7 +8766,7 @@
     </row>
     <row r="462" spans="1:4">
       <c r="A462" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B462">
         <v>6</v>
@@ -8337,7 +8780,7 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B463">
         <v>6</v>
@@ -8351,7 +8794,7 @@
     </row>
     <row r="464" spans="1:4">
       <c r="A464" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B464">
         <v>6</v>
@@ -8365,7 +8808,7 @@
     </row>
     <row r="465" spans="1:4">
       <c r="A465" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B465">
         <v>6</v>
@@ -8379,7 +8822,7 @@
     </row>
     <row r="466" spans="1:4">
       <c r="A466" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B466">
         <v>6</v>
@@ -8393,7 +8836,7 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B467">
         <v>6</v>
@@ -8407,7 +8850,7 @@
     </row>
     <row r="468" spans="1:4">
       <c r="A468" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B468">
         <v>6</v>
@@ -8421,7 +8864,7 @@
     </row>
     <row r="469" spans="1:4">
       <c r="A469" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B469">
         <v>6</v>
@@ -8435,7 +8878,7 @@
     </row>
     <row r="470" spans="1:4">
       <c r="A470" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B470">
         <v>6</v>
@@ -8449,7 +8892,7 @@
     </row>
     <row r="471" spans="1:4">
       <c r="A471" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B471">
         <v>6</v>
@@ -8463,7 +8906,7 @@
     </row>
     <row r="472" spans="1:4">
       <c r="A472" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B472">
         <v>6</v>
@@ -8477,7 +8920,7 @@
     </row>
     <row r="473" spans="1:4">
       <c r="A473" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B473">
         <v>6</v>
@@ -8491,7 +8934,7 @@
     </row>
     <row r="474" spans="1:4">
       <c r="A474" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B474">
         <v>6</v>
@@ -8505,7 +8948,7 @@
     </row>
     <row r="475" spans="1:4">
       <c r="A475" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B475">
         <v>6</v>
@@ -8519,7 +8962,7 @@
     </row>
     <row r="476" spans="1:4">
       <c r="A476" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B476">
         <v>6</v>
@@ -8533,7 +8976,7 @@
     </row>
     <row r="477" spans="1:4">
       <c r="A477" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B477">
         <v>6</v>
@@ -8547,7 +8990,7 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B478">
         <v>6</v>
@@ -8561,7 +9004,7 @@
     </row>
     <row r="479" spans="1:4">
       <c r="A479" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B479">
         <v>6</v>
@@ -8575,7 +9018,7 @@
     </row>
     <row r="480" spans="1:4">
       <c r="A480" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B480">
         <v>6</v>
@@ -8589,7 +9032,7 @@
     </row>
     <row r="481" spans="1:4">
       <c r="A481" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B481">
         <v>6</v>
@@ -8603,7 +9046,7 @@
     </row>
     <row r="482" spans="1:4">
       <c r="A482" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B482">
         <v>6</v>
@@ -8617,21 +9060,21 @@
     </row>
     <row r="483" spans="1:4">
       <c r="A483" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B483">
         <v>6</v>
       </c>
       <c r="C483">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="D483">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="484" spans="1:4">
       <c r="A484" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B484">
         <v>6</v>
@@ -8645,7 +9088,7 @@
     </row>
     <row r="485" spans="1:4">
       <c r="A485" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B485">
         <v>6</v>
@@ -8659,7 +9102,7 @@
     </row>
     <row r="486" spans="1:4">
       <c r="A486" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B486">
         <v>6</v>
@@ -8673,7 +9116,7 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B487">
         <v>6</v>
@@ -8687,7 +9130,7 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B488">
         <v>6</v>
@@ -8701,7 +9144,7 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B489">
         <v>6</v>
@@ -8715,7 +9158,7 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B490">
         <v>6</v>
@@ -8729,7 +9172,7 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B491">
         <v>6</v>
@@ -8743,7 +9186,7 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B492">
         <v>6</v>
@@ -8757,7 +9200,7 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B493">
         <v>6</v>
@@ -8771,7 +9214,7 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B494">
         <v>6</v>
@@ -8785,7 +9228,7 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B495">
         <v>6</v>
@@ -8799,7 +9242,7 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B496">
         <v>6</v>
@@ -8813,7 +9256,7 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B497">
         <v>6</v>
@@ -8827,7 +9270,7 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B498">
         <v>6</v>
@@ -8841,7 +9284,7 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B499">
         <v>6</v>
@@ -8855,7 +9298,7 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B500">
         <v>6</v>
@@ -8869,7 +9312,7 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B501">
         <v>6</v>
@@ -8883,7 +9326,7 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B502">
         <v>6</v>
@@ -8896,8 +9339,8 @@
       </c>
     </row>
     <row r="503" spans="1:4">
-      <c r="A503" s="1">
-        <v>46049</v>
+      <c r="A503" t="s">
+        <v>501</v>
       </c>
       <c r="B503">
         <v>6</v>
@@ -8907,6 +9350,2064 @@
       </c>
       <c r="D503">
         <v>12.1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" t="s">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>6</v>
+      </c>
+      <c r="C504">
+        <v>2.6</v>
+      </c>
+      <c r="D504">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" t="s">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>6</v>
+      </c>
+      <c r="C505">
+        <v>2.6</v>
+      </c>
+      <c r="D505">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" t="s">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>6</v>
+      </c>
+      <c r="C506">
+        <v>2.6</v>
+      </c>
+      <c r="D506">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" t="s">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>6</v>
+      </c>
+      <c r="C507">
+        <v>2.6</v>
+      </c>
+      <c r="D507">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" t="s">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>6</v>
+      </c>
+      <c r="C508">
+        <v>2.6</v>
+      </c>
+      <c r="D508">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" t="s">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>6</v>
+      </c>
+      <c r="C509">
+        <v>2.6</v>
+      </c>
+      <c r="D509">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" t="s">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>6</v>
+      </c>
+      <c r="C510">
+        <v>2.6</v>
+      </c>
+      <c r="D510">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" t="s">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>6</v>
+      </c>
+      <c r="C511">
+        <v>2.6</v>
+      </c>
+      <c r="D511">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" t="s">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>6</v>
+      </c>
+      <c r="C512">
+        <v>2.6</v>
+      </c>
+      <c r="D512">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" t="s">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>6</v>
+      </c>
+      <c r="C513">
+        <v>2.6</v>
+      </c>
+      <c r="D513">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" t="s">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>6</v>
+      </c>
+      <c r="C514">
+        <v>2.6</v>
+      </c>
+      <c r="D514">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" t="s">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>6</v>
+      </c>
+      <c r="C515">
+        <v>2.6</v>
+      </c>
+      <c r="D515">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" t="s">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>6</v>
+      </c>
+      <c r="C516">
+        <v>2.6</v>
+      </c>
+      <c r="D516">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" t="s">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>6</v>
+      </c>
+      <c r="C517">
+        <v>2.6</v>
+      </c>
+      <c r="D517">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" t="s">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>6</v>
+      </c>
+      <c r="C518">
+        <v>2.6</v>
+      </c>
+      <c r="D518">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" t="s">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>6</v>
+      </c>
+      <c r="C519">
+        <v>2.6</v>
+      </c>
+      <c r="D519">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" t="s">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>6</v>
+      </c>
+      <c r="C520">
+        <v>2.6</v>
+      </c>
+      <c r="D520">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" t="s">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>6</v>
+      </c>
+      <c r="C521">
+        <v>2.6</v>
+      </c>
+      <c r="D521">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
+      <c r="A522" t="s">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>6</v>
+      </c>
+      <c r="C522">
+        <v>2.6</v>
+      </c>
+      <c r="D522">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
+      <c r="A523" t="s">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>6</v>
+      </c>
+      <c r="C523">
+        <v>2.6</v>
+      </c>
+      <c r="D523">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4">
+      <c r="A524" t="s">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>6</v>
+      </c>
+      <c r="C524">
+        <v>2.6</v>
+      </c>
+      <c r="D524">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
+      <c r="A525" t="s">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>6</v>
+      </c>
+      <c r="C525">
+        <v>2.6</v>
+      </c>
+      <c r="D525">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
+      <c r="A526" t="s">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>6</v>
+      </c>
+      <c r="C526">
+        <v>2.7</v>
+      </c>
+      <c r="D526">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
+      <c r="A527" t="s">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>6</v>
+      </c>
+      <c r="C527">
+        <v>2.7</v>
+      </c>
+      <c r="D527">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4">
+      <c r="A528" t="s">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>6</v>
+      </c>
+      <c r="C528">
+        <v>2.7</v>
+      </c>
+      <c r="D528">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4">
+      <c r="A529" t="s">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>6</v>
+      </c>
+      <c r="C529">
+        <v>2.7</v>
+      </c>
+      <c r="D529">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
+      <c r="A530" t="s">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>6</v>
+      </c>
+      <c r="C530">
+        <v>2.7</v>
+      </c>
+      <c r="D530">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4">
+      <c r="A531" t="s">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>6</v>
+      </c>
+      <c r="C531">
+        <v>2.7</v>
+      </c>
+      <c r="D531">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
+      <c r="A532" t="s">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>6</v>
+      </c>
+      <c r="C532">
+        <v>2.7</v>
+      </c>
+      <c r="D532">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4">
+      <c r="A533" t="s">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>6</v>
+      </c>
+      <c r="C533">
+        <v>2.7</v>
+      </c>
+      <c r="D533">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
+      <c r="A534" t="s">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>6</v>
+      </c>
+      <c r="C534">
+        <v>2.7</v>
+      </c>
+      <c r="D534">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4">
+      <c r="A535" t="s">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>6</v>
+      </c>
+      <c r="C535">
+        <v>2.7</v>
+      </c>
+      <c r="D535">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4">
+      <c r="A536" t="s">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>6</v>
+      </c>
+      <c r="C536">
+        <v>2.7</v>
+      </c>
+      <c r="D536">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4">
+      <c r="A537" t="s">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>6</v>
+      </c>
+      <c r="C537">
+        <v>2.7</v>
+      </c>
+      <c r="D537">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
+      <c r="A538" t="s">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>6</v>
+      </c>
+      <c r="C538">
+        <v>2.7</v>
+      </c>
+      <c r="D538">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
+      <c r="A539" t="s">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>6</v>
+      </c>
+      <c r="C539">
+        <v>2.7</v>
+      </c>
+      <c r="D539">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4">
+      <c r="A540" t="s">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>6</v>
+      </c>
+      <c r="C540">
+        <v>2.7</v>
+      </c>
+      <c r="D540">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4">
+      <c r="A541" t="s">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>6</v>
+      </c>
+      <c r="C541">
+        <v>2.7</v>
+      </c>
+      <c r="D541">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
+      <c r="A542" t="s">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>6</v>
+      </c>
+      <c r="C542">
+        <v>2.7</v>
+      </c>
+      <c r="D542">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4">
+      <c r="A543" t="s">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>6</v>
+      </c>
+      <c r="C543">
+        <v>2.7</v>
+      </c>
+      <c r="D543">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
+      <c r="A544" t="s">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>6</v>
+      </c>
+      <c r="C544">
+        <v>2.7</v>
+      </c>
+      <c r="D544">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4">
+      <c r="A545" t="s">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>6</v>
+      </c>
+      <c r="C545">
+        <v>2.7</v>
+      </c>
+      <c r="D545">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4">
+      <c r="A546" t="s">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>6</v>
+      </c>
+      <c r="C546">
+        <v>2.7</v>
+      </c>
+      <c r="D546">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4">
+      <c r="A547" t="s">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>6</v>
+      </c>
+      <c r="C547">
+        <v>2.7</v>
+      </c>
+      <c r="D547">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4">
+      <c r="A548" t="s">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>6</v>
+      </c>
+      <c r="C548">
+        <v>2.7</v>
+      </c>
+      <c r="D548">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4">
+      <c r="A549" t="s">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>6.1</v>
+      </c>
+      <c r="C549">
+        <v>2.7</v>
+      </c>
+      <c r="D549">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4">
+      <c r="A550" t="s">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>6.1</v>
+      </c>
+      <c r="C550">
+        <v>2.7</v>
+      </c>
+      <c r="D550">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4">
+      <c r="A551" t="s">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>6.1</v>
+      </c>
+      <c r="C551">
+        <v>2.7</v>
+      </c>
+      <c r="D551">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4">
+      <c r="A552" t="s">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>6.1</v>
+      </c>
+      <c r="C552">
+        <v>2.7</v>
+      </c>
+      <c r="D552">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4">
+      <c r="A553" t="s">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>6.1</v>
+      </c>
+      <c r="C553">
+        <v>2.7</v>
+      </c>
+      <c r="D553">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4">
+      <c r="A554" t="s">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>6.1</v>
+      </c>
+      <c r="C554">
+        <v>2.7</v>
+      </c>
+      <c r="D554">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4">
+      <c r="A555" t="s">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>6.1</v>
+      </c>
+      <c r="C555">
+        <v>2.7</v>
+      </c>
+      <c r="D555">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4">
+      <c r="A556" t="s">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>6.1</v>
+      </c>
+      <c r="C556">
+        <v>2.7</v>
+      </c>
+      <c r="D556">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4">
+      <c r="A557" t="s">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>6.1</v>
+      </c>
+      <c r="C557">
+        <v>2.7</v>
+      </c>
+      <c r="D557">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4">
+      <c r="A558" t="s">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>6.1</v>
+      </c>
+      <c r="C558">
+        <v>2.7</v>
+      </c>
+      <c r="D558">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4">
+      <c r="A559" t="s">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>6.1</v>
+      </c>
+      <c r="C559">
+        <v>2.7</v>
+      </c>
+      <c r="D559">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4">
+      <c r="A560" t="s">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>6.1</v>
+      </c>
+      <c r="C560">
+        <v>2.7</v>
+      </c>
+      <c r="D560">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4">
+      <c r="A561" t="s">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>6.1</v>
+      </c>
+      <c r="C561">
+        <v>2.7</v>
+      </c>
+      <c r="D561">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4">
+      <c r="A562" t="s">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>6.1</v>
+      </c>
+      <c r="C562">
+        <v>2.7</v>
+      </c>
+      <c r="D562">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4">
+      <c r="A563" t="s">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>6.1</v>
+      </c>
+      <c r="C563">
+        <v>2.7</v>
+      </c>
+      <c r="D563">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4">
+      <c r="A564" t="s">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>6.1</v>
+      </c>
+      <c r="C564">
+        <v>2.7</v>
+      </c>
+      <c r="D564">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4">
+      <c r="A565" t="s">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>6.1</v>
+      </c>
+      <c r="C565">
+        <v>2.7</v>
+      </c>
+      <c r="D565">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4">
+      <c r="A566" t="s">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>6.1</v>
+      </c>
+      <c r="C566">
+        <v>2.7</v>
+      </c>
+      <c r="D566">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4">
+      <c r="A567" t="s">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>6.1</v>
+      </c>
+      <c r="C567">
+        <v>2.7</v>
+      </c>
+      <c r="D567">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
+      <c r="A568" t="s">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>6.1</v>
+      </c>
+      <c r="C568">
+        <v>2.7</v>
+      </c>
+      <c r="D568">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4">
+      <c r="A569" t="s">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>6.1</v>
+      </c>
+      <c r="C569">
+        <v>2.7</v>
+      </c>
+      <c r="D569">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
+      <c r="A570" t="s">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>6.1</v>
+      </c>
+      <c r="C570">
+        <v>2.7</v>
+      </c>
+      <c r="D570">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
+      <c r="A571" t="s">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>6.1</v>
+      </c>
+      <c r="C571">
+        <v>2.7</v>
+      </c>
+      <c r="D571">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4">
+      <c r="A572" t="s">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>6.1</v>
+      </c>
+      <c r="C572">
+        <v>2.7</v>
+      </c>
+      <c r="D572">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4">
+      <c r="A573" t="s">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>6.1</v>
+      </c>
+      <c r="C573">
+        <v>2.7</v>
+      </c>
+      <c r="D573">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4">
+      <c r="A574" t="s">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>6.1</v>
+      </c>
+      <c r="C574">
+        <v>2.7</v>
+      </c>
+      <c r="D574">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4">
+      <c r="A575" t="s">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>6.1</v>
+      </c>
+      <c r="C575">
+        <v>2.7</v>
+      </c>
+      <c r="D575">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4">
+      <c r="A576" t="s">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>6.1</v>
+      </c>
+      <c r="C576">
+        <v>2.7</v>
+      </c>
+      <c r="D576">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4">
+      <c r="A577" t="s">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>6.1</v>
+      </c>
+      <c r="C577">
+        <v>2.7</v>
+      </c>
+      <c r="D577">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4">
+      <c r="A578" t="s">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>6.1</v>
+      </c>
+      <c r="C578">
+        <v>2.7</v>
+      </c>
+      <c r="D578">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4">
+      <c r="A579" t="s">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>6.1</v>
+      </c>
+      <c r="C579">
+        <v>2.7</v>
+      </c>
+      <c r="D579">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4">
+      <c r="A580" t="s">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>6.1</v>
+      </c>
+      <c r="C580">
+        <v>2.7</v>
+      </c>
+      <c r="D580">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4">
+      <c r="A581" t="s">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>6.1</v>
+      </c>
+      <c r="C581">
+        <v>2.7</v>
+      </c>
+      <c r="D581">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4">
+      <c r="A582" t="s">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>6.1</v>
+      </c>
+      <c r="C582">
+        <v>2.7</v>
+      </c>
+      <c r="D582">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4">
+      <c r="A583" t="s">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>6.1</v>
+      </c>
+      <c r="C583">
+        <v>2.7</v>
+      </c>
+      <c r="D583">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4">
+      <c r="A584" t="s">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>6.1</v>
+      </c>
+      <c r="C584">
+        <v>2.7</v>
+      </c>
+      <c r="D584">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4">
+      <c r="A585" t="s">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>6.1</v>
+      </c>
+      <c r="C585">
+        <v>2.7</v>
+      </c>
+      <c r="D585">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4">
+      <c r="A586" t="s">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>6.1</v>
+      </c>
+      <c r="C586">
+        <v>2.7</v>
+      </c>
+      <c r="D586">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4">
+      <c r="A587" t="s">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>6.1</v>
+      </c>
+      <c r="C587">
+        <v>2.7</v>
+      </c>
+      <c r="D587">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4">
+      <c r="A588" t="s">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>6.1</v>
+      </c>
+      <c r="C588">
+        <v>2.7</v>
+      </c>
+      <c r="D588">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4">
+      <c r="A589" t="s">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>6.1</v>
+      </c>
+      <c r="C589">
+        <v>2.7</v>
+      </c>
+      <c r="D589">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4">
+      <c r="A590" t="s">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>6.1</v>
+      </c>
+      <c r="C590">
+        <v>2.7</v>
+      </c>
+      <c r="D590">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4">
+      <c r="A591" t="s">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>6.1</v>
+      </c>
+      <c r="C591">
+        <v>2.7</v>
+      </c>
+      <c r="D591">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4">
+      <c r="A592" t="s">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>6.1</v>
+      </c>
+      <c r="C592">
+        <v>2.7</v>
+      </c>
+      <c r="D592">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4">
+      <c r="A593" t="s">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>6</v>
+      </c>
+      <c r="C593">
+        <v>2.7</v>
+      </c>
+      <c r="D593">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4">
+      <c r="A594" t="s">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>6</v>
+      </c>
+      <c r="C594">
+        <v>2.7</v>
+      </c>
+      <c r="D594">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4">
+      <c r="A595" t="s">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>6</v>
+      </c>
+      <c r="C595">
+        <v>2.7</v>
+      </c>
+      <c r="D595">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4">
+      <c r="A596" t="s">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>6</v>
+      </c>
+      <c r="C596">
+        <v>2.7</v>
+      </c>
+      <c r="D596">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4">
+      <c r="A597" t="s">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>6</v>
+      </c>
+      <c r="C597">
+        <v>2.7</v>
+      </c>
+      <c r="D597">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4">
+      <c r="A598" t="s">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>6</v>
+      </c>
+      <c r="C598">
+        <v>2.7</v>
+      </c>
+      <c r="D598">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4">
+      <c r="A599" t="s">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>6</v>
+      </c>
+      <c r="C599">
+        <v>2.7</v>
+      </c>
+      <c r="D599">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4">
+      <c r="A600" t="s">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>6</v>
+      </c>
+      <c r="C600">
+        <v>2.7</v>
+      </c>
+      <c r="D600">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4">
+      <c r="A601" t="s">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>6</v>
+      </c>
+      <c r="C601">
+        <v>2.7</v>
+      </c>
+      <c r="D601">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4">
+      <c r="A602" t="s">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>6</v>
+      </c>
+      <c r="C602">
+        <v>2.7</v>
+      </c>
+      <c r="D602">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4">
+      <c r="A603" t="s">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>6</v>
+      </c>
+      <c r="C603">
+        <v>2.7</v>
+      </c>
+      <c r="D603">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4">
+      <c r="A604" t="s">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>6</v>
+      </c>
+      <c r="C604">
+        <v>2.7</v>
+      </c>
+      <c r="D604">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4">
+      <c r="A605" t="s">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>6</v>
+      </c>
+      <c r="C605">
+        <v>2.7</v>
+      </c>
+      <c r="D605">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4">
+      <c r="A606" t="s">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>6</v>
+      </c>
+      <c r="C606">
+        <v>2.7</v>
+      </c>
+      <c r="D606">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4">
+      <c r="A607" t="s">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>6</v>
+      </c>
+      <c r="C607">
+        <v>2.7</v>
+      </c>
+      <c r="D607">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4">
+      <c r="A608" t="s">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>6</v>
+      </c>
+      <c r="C608">
+        <v>2.7</v>
+      </c>
+      <c r="D608">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4">
+      <c r="A609" t="s">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>6</v>
+      </c>
+      <c r="C609">
+        <v>2.7</v>
+      </c>
+      <c r="D609">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4">
+      <c r="A610" t="s">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>6</v>
+      </c>
+      <c r="C610">
+        <v>2.7</v>
+      </c>
+      <c r="D610">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4">
+      <c r="A611" t="s">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>6</v>
+      </c>
+      <c r="C611">
+        <v>2.7</v>
+      </c>
+      <c r="D611">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4">
+      <c r="A612" t="s">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>6</v>
+      </c>
+      <c r="C612">
+        <v>2.7</v>
+      </c>
+      <c r="D612">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4">
+      <c r="A613" t="s">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>6</v>
+      </c>
+      <c r="C613">
+        <v>2.7</v>
+      </c>
+      <c r="D613">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4">
+      <c r="A614" t="s">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>6</v>
+      </c>
+      <c r="C614">
+        <v>2.7</v>
+      </c>
+      <c r="D614">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4">
+      <c r="A615" t="s">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>6</v>
+      </c>
+      <c r="C615">
+        <v>2.7</v>
+      </c>
+      <c r="D615">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4">
+      <c r="A616" t="s">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>6</v>
+      </c>
+      <c r="C616">
+        <v>2.7</v>
+      </c>
+      <c r="D616">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4">
+      <c r="A617" t="s">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>6</v>
+      </c>
+      <c r="C617">
+        <v>2.7</v>
+      </c>
+      <c r="D617">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4">
+      <c r="A618" t="s">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>6</v>
+      </c>
+      <c r="C618">
+        <v>2.7</v>
+      </c>
+      <c r="D618">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4">
+      <c r="A619" t="s">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>6</v>
+      </c>
+      <c r="C619">
+        <v>2.7</v>
+      </c>
+      <c r="D619">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4">
+      <c r="A620" t="s">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>6</v>
+      </c>
+      <c r="C620">
+        <v>2.7</v>
+      </c>
+      <c r="D620">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4">
+      <c r="A621" t="s">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>6</v>
+      </c>
+      <c r="C621">
+        <v>2.7</v>
+      </c>
+      <c r="D621">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4">
+      <c r="A622" t="s">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>6</v>
+      </c>
+      <c r="C622">
+        <v>2.7</v>
+      </c>
+      <c r="D622">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4">
+      <c r="A623" t="s">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>6</v>
+      </c>
+      <c r="C623">
+        <v>2.7</v>
+      </c>
+      <c r="D623">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4">
+      <c r="A624" t="s">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>6</v>
+      </c>
+      <c r="C624">
+        <v>2.7</v>
+      </c>
+      <c r="D624">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4">
+      <c r="A625" t="s">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>6</v>
+      </c>
+      <c r="C625">
+        <v>2.7</v>
+      </c>
+      <c r="D625">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4">
+      <c r="A626" t="s">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>6</v>
+      </c>
+      <c r="C626">
+        <v>2.7</v>
+      </c>
+      <c r="D626">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4">
+      <c r="A627" t="s">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>6</v>
+      </c>
+      <c r="C627">
+        <v>2.7</v>
+      </c>
+      <c r="D627">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4">
+      <c r="A628" t="s">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>6</v>
+      </c>
+      <c r="C628">
+        <v>2.7</v>
+      </c>
+      <c r="D628">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4">
+      <c r="A629" t="s">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>6</v>
+      </c>
+      <c r="C629">
+        <v>2.7</v>
+      </c>
+      <c r="D629">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4">
+      <c r="A630" t="s">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>6</v>
+      </c>
+      <c r="C630">
+        <v>2.7</v>
+      </c>
+      <c r="D630">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4">
+      <c r="A631" t="s">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>6</v>
+      </c>
+      <c r="C631">
+        <v>2.7</v>
+      </c>
+      <c r="D631">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4">
+      <c r="A632" t="s">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>6</v>
+      </c>
+      <c r="C632">
+        <v>2.7</v>
+      </c>
+      <c r="D632">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4">
+      <c r="A633" t="s">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>6</v>
+      </c>
+      <c r="C633">
+        <v>2.7</v>
+      </c>
+      <c r="D633">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4">
+      <c r="A634" t="s">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>6</v>
+      </c>
+      <c r="C634">
+        <v>2.7</v>
+      </c>
+      <c r="D634">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4">
+      <c r="A635" t="s">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>6</v>
+      </c>
+      <c r="C635">
+        <v>2.7</v>
+      </c>
+      <c r="D635">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4">
+      <c r="A636" t="s">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>6</v>
+      </c>
+      <c r="C636">
+        <v>2.7</v>
+      </c>
+      <c r="D636">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4">
+      <c r="A637" t="s">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>6</v>
+      </c>
+      <c r="C637">
+        <v>2.7</v>
+      </c>
+      <c r="D637">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4">
+      <c r="A638" t="s">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>6</v>
+      </c>
+      <c r="C638">
+        <v>2.7</v>
+      </c>
+      <c r="D638">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4">
+      <c r="A639" t="s">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>6</v>
+      </c>
+      <c r="C639">
+        <v>2.7</v>
+      </c>
+      <c r="D639">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4">
+      <c r="A640" t="s">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>6</v>
+      </c>
+      <c r="C640">
+        <v>2.7</v>
+      </c>
+      <c r="D640">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4">
+      <c r="A641" t="s">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>6</v>
+      </c>
+      <c r="C641">
+        <v>2.7</v>
+      </c>
+      <c r="D641">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4">
+      <c r="A642" t="s">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>6</v>
+      </c>
+      <c r="C642">
+        <v>2.7</v>
+      </c>
+      <c r="D642">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4">
+      <c r="A643" t="s">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>6</v>
+      </c>
+      <c r="C643">
+        <v>2.7</v>
+      </c>
+      <c r="D643">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4">
+      <c r="A644" t="s">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>6</v>
+      </c>
+      <c r="C644">
+        <v>2.7</v>
+      </c>
+      <c r="D644">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4">
+      <c r="A645" t="s">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>6</v>
+      </c>
+      <c r="C645">
+        <v>2.7</v>
+      </c>
+      <c r="D645">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4">
+      <c r="A646" t="s">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>6</v>
+      </c>
+      <c r="C646">
+        <v>2.7</v>
+      </c>
+      <c r="D646">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4">
+      <c r="A647" t="s">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>6</v>
+      </c>
+      <c r="C647">
+        <v>2.7</v>
+      </c>
+      <c r="D647">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4">
+      <c r="A648" t="s">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>6</v>
+      </c>
+      <c r="C648">
+        <v>2.7</v>
+      </c>
+      <c r="D648">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4">
+      <c r="A649" t="s">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>6</v>
+      </c>
+      <c r="C649">
+        <v>2.7</v>
+      </c>
+      <c r="D649">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4">
+      <c r="A650" t="s">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>6</v>
+      </c>
+      <c r="C650">
+        <v>2.7</v>
+      </c>
+      <c r="D650">
+        <v>11.8</v>
       </c>
     </row>
   </sheetData>

--- a/Master/Master_DATA.xlsx
+++ b/Master/Master_DATA.xlsx
@@ -1,24 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="657">
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>VANGUARDDD.INTERMEDIATETERMCORPORATEBONDETF.AVGDURATION.B</t>
+  </si>
+  <si>
+    <t>VANGUARDDD.SHORTTERMCORPORATEBONDETF.AVGDURATION.B</t>
+  </si>
+  <si>
+    <t>VANGUARDDD.LONGTERMCORPORATEBONDETF.AVGDURATION.B</t>
+  </si>
+  <si>
+    <t>Vanguard Intermediate-Term Corporate Bond ETF</t>
+  </si>
+  <si>
+    <t>Vanguard Short-Term Corporate Bond ETF</t>
+  </si>
+  <si>
+    <t>Vanguard Long-Term Corporate Bond ETF</t>
+  </si>
+  <si>
     <t>2024-02-29</t>
   </si>
   <si>
@@ -1963,35 +1978,23 @@
     <t>2026-08-19</t>
   </si>
   <si>
-    <t>VANGUARDDD.INTERMEDIATETERMCORPORATEBONDETF.AVGDURATION.B</t>
-  </si>
-  <si>
-    <t>Vanguard Intermediate-Term Corporate Bond ETF</t>
-  </si>
-  <si>
-    <t>VANGUARDDD.SHORTTERMCORPORATEBONDETF.AVGDURATION.B</t>
-  </si>
-  <si>
-    <t>Vanguard Short-Term Corporate Bond ETF</t>
-  </si>
-  <si>
-    <t>VANGUARDDD.LONGTERMCORPORATEBONDETF.AVGDURATION.B</t>
-  </si>
-  <si>
-    <t>Vanguard Long-Term Corporate Bond ETF</t>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2021,7 +2024,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2100,6 +2111,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2134,6 +2146,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2168,20 +2181,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2303,44 +2312,86 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D650"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D653"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>649</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>651</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>650</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>652</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>6.1</v>
@@ -2352,9 +2403,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>6.1</v>
@@ -2366,9 +2417,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>6.1</v>
@@ -2380,9 +2431,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>6.1</v>
@@ -2394,9 +2445,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>6.1</v>
@@ -2408,9 +2459,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>6.1</v>
@@ -2422,9 +2473,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>6.1</v>
@@ -2436,9 +2487,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>6.1</v>
@@ -2450,9 +2501,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>6.1</v>
@@ -2464,9 +2515,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>6.1</v>
@@ -2478,9 +2529,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>6.1</v>
@@ -2492,9 +2543,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>6.1</v>
@@ -2506,9 +2557,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>6.1</v>
@@ -2520,9 +2571,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>6.1</v>
@@ -2534,9 +2585,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>6.1</v>
@@ -2548,9 +2599,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>6.1</v>
@@ -2562,9 +2613,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>6.1</v>
@@ -2576,9 +2627,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>6.1</v>
@@ -2590,9 +2641,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>6.1</v>
@@ -2604,9 +2655,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>6.1</v>
@@ -2618,9 +2669,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>6.1</v>
@@ -2632,9 +2683,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>6.1</v>
@@ -2646,9 +2697,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B25">
         <v>6.1</v>
@@ -2660,9 +2711,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B26">
         <v>6.1</v>
@@ -2674,9 +2725,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>6.1</v>
@@ -2688,9 +2739,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>6.1</v>
@@ -2702,9 +2753,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>6.1</v>
@@ -2716,9 +2767,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>6.1</v>
@@ -2730,9 +2781,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>6.1</v>
@@ -2744,9 +2795,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>6.1</v>
@@ -2758,9 +2809,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>6.1</v>
@@ -2772,9 +2823,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B34">
         <v>6.1</v>
@@ -2786,9 +2837,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B35">
         <v>6.1</v>
@@ -2800,9 +2851,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B36">
         <v>6.1</v>
@@ -2814,9 +2865,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B37">
         <v>6.1</v>
@@ -2828,9 +2879,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B38">
         <v>6.1</v>
@@ -2842,9 +2893,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B39">
         <v>6.1</v>
@@ -2856,9 +2907,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B40">
         <v>6.1</v>
@@ -2870,9 +2921,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B41">
         <v>6.1</v>
@@ -2884,9 +2935,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B42">
         <v>6.1</v>
@@ -2898,9 +2949,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B43">
         <v>6.1</v>
@@ -2912,9 +2963,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B44">
         <v>6.1</v>
@@ -2926,9 +2977,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B45">
         <v>6.1</v>
@@ -2940,9 +2991,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B46">
         <v>6.1</v>
@@ -2954,9 +3005,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B47">
         <v>6.1</v>
@@ -2968,9 +3019,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>6.1</v>
@@ -2982,9 +3033,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B49">
         <v>6.1</v>
@@ -2996,9 +3047,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>6.1</v>
@@ -3010,9 +3061,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B51">
         <v>6.1</v>
@@ -3024,9 +3075,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B52">
         <v>6.1</v>
@@ -3038,9 +3089,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B53">
         <v>6.1</v>
@@ -3052,9 +3103,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>6.1</v>
@@ -3066,9 +3117,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B55">
         <v>6.1</v>
@@ -3080,9 +3131,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B56">
         <v>6.1</v>
@@ -3094,9 +3145,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B57">
         <v>6.1</v>
@@ -3108,9 +3159,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B58">
         <v>6.1</v>
@@ -3122,9 +3173,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B59">
         <v>6.1</v>
@@ -3136,9 +3187,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B60">
         <v>6.1</v>
@@ -3150,9 +3201,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B61">
         <v>6.1</v>
@@ -3164,9 +3215,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B62">
         <v>6.1</v>
@@ -3178,9 +3229,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B63">
         <v>6.1</v>
@@ -3192,9 +3243,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B64">
         <v>6.1</v>
@@ -3206,9 +3257,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B65">
         <v>6.1</v>
@@ -3220,9 +3271,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B66">
         <v>6.1</v>
@@ -3234,9 +3285,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B67">
         <v>6.1</v>
@@ -3248,9 +3299,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B68">
         <v>6.1</v>
@@ -3262,9 +3313,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B69">
         <v>6.1</v>
@@ -3276,9 +3327,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B70">
         <v>6.1</v>
@@ -3290,9 +3341,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B71">
         <v>6.1</v>
@@ -3304,9 +3355,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B72">
         <v>6.1</v>
@@ -3318,9 +3369,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B73">
         <v>6.1</v>
@@ -3332,9 +3383,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B74">
         <v>6.1</v>
@@ -3346,9 +3397,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B75">
         <v>6.1</v>
@@ -3360,9 +3411,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B76">
         <v>6.1</v>
@@ -3374,9 +3425,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B77">
         <v>6.1</v>
@@ -3388,9 +3439,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B78">
         <v>6.1</v>
@@ -3402,9 +3453,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B79">
         <v>6.1</v>
@@ -3416,9 +3467,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B80">
         <v>6.1</v>
@@ -3430,9 +3481,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B81">
         <v>6.1</v>
@@ -3444,9 +3495,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B82">
         <v>6.1</v>
@@ -3458,9 +3509,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B83">
         <v>6.1</v>
@@ -3472,9 +3523,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B84">
         <v>6.1</v>
@@ -3486,9 +3537,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B85">
         <v>6.1</v>
@@ -3500,9 +3551,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B86">
         <v>6.1</v>
@@ -3514,9 +3565,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B87">
         <v>6.1</v>
@@ -3528,9 +3579,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B88">
         <v>6.1</v>
@@ -3542,9 +3593,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B89">
         <v>6.1</v>
@@ -3556,9 +3607,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B90">
         <v>6.1</v>
@@ -3570,9 +3621,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B91">
         <v>6.1</v>
@@ -3584,9 +3635,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B92">
         <v>6.1</v>
@@ -3598,9 +3649,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B93">
         <v>6.1</v>
@@ -3612,9 +3663,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B94">
         <v>6.1</v>
@@ -3626,9 +3677,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B95">
         <v>6.1</v>
@@ -3640,9 +3691,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B96">
         <v>6.1</v>
@@ -3654,9 +3705,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B97">
         <v>6.1</v>
@@ -3668,9 +3719,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B98">
         <v>6.1</v>
@@ -3682,9 +3733,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B99">
         <v>6.1</v>
@@ -3696,9 +3747,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B100">
         <v>6.1</v>
@@ -3710,9 +3761,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B101">
         <v>6.1</v>
@@ -3724,9 +3775,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B102">
         <v>6.1</v>
@@ -3738,9 +3789,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B103">
         <v>6.1</v>
@@ -3752,9 +3803,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B104">
         <v>6.1</v>
@@ -3766,9 +3817,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B105">
         <v>6.1</v>
@@ -3780,9 +3831,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B106">
         <v>6.1</v>
@@ -3794,9 +3845,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B107">
         <v>6.1</v>
@@ -3808,9 +3859,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B108">
         <v>6.1</v>
@@ -3822,9 +3873,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B109">
         <v>6.1</v>
@@ -3836,9 +3887,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B110">
         <v>6.1</v>
@@ -3850,9 +3901,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B111">
         <v>6.1</v>
@@ -3864,9 +3915,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B112">
         <v>6.1</v>
@@ -3878,9 +3929,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B113">
         <v>6.1</v>
@@ -3892,9 +3943,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B114">
         <v>6.1</v>
@@ -3906,9 +3957,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B115">
         <v>6.1</v>
@@ -3920,9 +3971,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B116">
         <v>6.1</v>
@@ -3934,9 +3985,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B117">
         <v>6.1</v>
@@ -3948,9 +3999,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B118">
         <v>6.1</v>
@@ -3962,9 +4013,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B119">
         <v>6.1</v>
@@ -3976,9 +4027,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B120">
         <v>6.1</v>
@@ -3990,9 +4041,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B121">
         <v>6.1</v>
@@ -4004,9 +4055,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B122">
         <v>6.1</v>
@@ -4018,9 +4069,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B123">
         <v>6.1</v>
@@ -4032,9 +4083,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B124">
         <v>6.1</v>
@@ -4046,9 +4097,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B125">
         <v>6.1</v>
@@ -4060,9 +4111,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B126">
         <v>6.1</v>
@@ -4074,9 +4125,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B127">
         <v>6.1</v>
@@ -4088,9 +4139,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B128">
         <v>6.1</v>
@@ -4102,9 +4153,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B129">
         <v>6.1</v>
@@ -4116,9 +4167,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B130">
         <v>6.1</v>
@@ -4130,9 +4181,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B131">
         <v>6.1</v>
@@ -4144,9 +4195,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B132">
         <v>6.1</v>
@@ -4158,9 +4209,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B133">
         <v>6.1</v>
@@ -4172,9 +4223,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B134">
         <v>6.1</v>
@@ -4186,9 +4237,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B135">
         <v>6.1</v>
@@ -4200,9 +4251,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B136">
         <v>6.1</v>
@@ -4214,9 +4265,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B137">
         <v>6.1</v>
@@ -4228,9 +4279,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B138">
         <v>6.1</v>
@@ -4242,9 +4293,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B139">
         <v>6.1</v>
@@ -4256,9 +4307,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B140">
         <v>6.1</v>
@@ -4270,9 +4321,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B141">
         <v>6.1</v>
@@ -4284,9 +4335,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B142">
         <v>6.1</v>
@@ -4298,9 +4349,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B143">
         <v>6.1</v>
@@ -4312,9 +4363,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B144">
         <v>6.1</v>
@@ -4326,9 +4377,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B145">
         <v>6.1</v>
@@ -4340,9 +4391,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B146">
         <v>6.1</v>
@@ -4354,9 +4405,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B147">
         <v>6.1</v>
@@ -4368,9 +4419,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B148">
         <v>6.1</v>
@@ -4382,9 +4433,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B149">
         <v>6.1</v>
@@ -4396,9 +4447,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B150">
         <v>6.1</v>
@@ -4410,9 +4461,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B151">
         <v>6.1</v>
@@ -4424,9 +4475,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B152">
         <v>6.1</v>
@@ -4438,9 +4489,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B153">
         <v>6.1</v>
@@ -4452,9 +4503,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B154">
         <v>6.1</v>
@@ -4466,9 +4517,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B155">
         <v>6.1</v>
@@ -4480,9 +4531,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B156">
         <v>6.1</v>
@@ -4494,9 +4545,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B157">
         <v>6.1</v>
@@ -4508,9 +4559,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B158">
         <v>6.1</v>
@@ -4522,9 +4573,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B159">
         <v>6.1</v>
@@ -4536,9 +4587,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B160">
         <v>6.1</v>
@@ -4550,9 +4601,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B161">
         <v>6.1</v>
@@ -4564,9 +4615,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B162">
         <v>6.1</v>
@@ -4578,9 +4629,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B163">
         <v>6.1</v>
@@ -4592,9 +4643,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B164">
         <v>6.1</v>
@@ -4606,9 +4657,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B165">
         <v>6.1</v>
@@ -4620,9 +4671,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B166">
         <v>6.1</v>
@@ -4634,9 +4685,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B167">
         <v>6.1</v>
@@ -4648,9 +4699,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B168">
         <v>6.1</v>
@@ -4662,9 +4713,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B169">
         <v>6.1</v>
@@ -4676,9 +4727,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B170">
         <v>6.1</v>
@@ -4690,9 +4741,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B171">
         <v>6.1</v>
@@ -4704,9 +4755,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B172">
         <v>6.1</v>
@@ -4718,9 +4769,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B173">
         <v>6.1</v>
@@ -4732,9 +4783,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B174">
         <v>6.1</v>
@@ -4746,9 +4797,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B175">
         <v>6.1</v>
@@ -4760,9 +4811,9 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B176">
         <v>6</v>
@@ -4774,9 +4825,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B177">
         <v>6</v>
@@ -4788,9 +4839,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B178">
         <v>6</v>
@@ -4802,9 +4853,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B179">
         <v>6</v>
@@ -4816,9 +4867,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B180">
         <v>6</v>
@@ -4830,9 +4881,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B181">
         <v>6</v>
@@ -4844,9 +4895,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B182">
         <v>6</v>
@@ -4858,9 +4909,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B183">
         <v>6</v>
@@ -4872,9 +4923,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B184">
         <v>6</v>
@@ -4886,9 +4937,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B185">
         <v>6</v>
@@ -4900,9 +4951,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B186">
         <v>6</v>
@@ -4914,9 +4965,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B187">
         <v>6</v>
@@ -4928,9 +4979,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B188">
         <v>6</v>
@@ -4942,9 +4993,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B189">
         <v>6</v>
@@ -4956,9 +5007,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B190">
         <v>6</v>
@@ -4970,9 +5021,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B191">
         <v>6</v>
@@ -4984,9 +5035,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B192">
         <v>6</v>
@@ -4998,9 +5049,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B193">
         <v>6</v>
@@ -5012,9 +5063,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B194">
         <v>6</v>
@@ -5026,9 +5077,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B195">
         <v>6</v>
@@ -5040,9 +5091,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B196">
         <v>6</v>
@@ -5054,9 +5105,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B197">
         <v>6</v>
@@ -5068,9 +5119,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B198">
         <v>6</v>
@@ -5082,9 +5133,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B199">
         <v>6</v>
@@ -5096,9 +5147,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B200">
         <v>6</v>
@@ -5110,9 +5161,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B201">
         <v>6</v>
@@ -5124,9 +5175,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B202">
         <v>6</v>
@@ -5138,9 +5189,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B203">
         <v>6</v>
@@ -5152,9 +5203,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B204">
         <v>6</v>
@@ -5166,9 +5217,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B205">
         <v>6</v>
@@ -5180,9 +5231,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B206">
         <v>6</v>
@@ -5194,9 +5245,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B207">
         <v>6</v>
@@ -5208,9 +5259,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B208">
         <v>6</v>
@@ -5222,9 +5273,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B209">
         <v>6</v>
@@ -5236,9 +5287,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="210" spans="1:4">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B210">
         <v>6</v>
@@ -5250,9 +5301,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B211">
         <v>6</v>
@@ -5264,9 +5315,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B212">
         <v>6</v>
@@ -5278,9 +5329,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B213">
         <v>6</v>
@@ -5292,9 +5343,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B214">
         <v>6</v>
@@ -5306,9 +5357,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B215">
         <v>6</v>
@@ -5320,9 +5371,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B216">
         <v>6</v>
@@ -5334,9 +5385,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B217">
         <v>6</v>
@@ -5348,9 +5399,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B218">
         <v>6</v>
@@ -5362,9 +5413,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B219">
         <v>5.9</v>
@@ -5376,9 +5427,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B220">
         <v>5.9</v>
@@ -5390,9 +5441,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B221">
         <v>5.9</v>
@@ -5404,9 +5455,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="222" spans="1:4">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B222">
         <v>5.9</v>
@@ -5418,9 +5469,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B223">
         <v>5.9</v>
@@ -5432,9 +5483,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B224">
         <v>5.9</v>
@@ -5446,9 +5497,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B225">
         <v>5.9</v>
@@ -5460,9 +5511,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B226">
         <v>5.9</v>
@@ -5474,9 +5525,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B227">
         <v>5.9</v>
@@ -5488,9 +5539,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B228">
         <v>5.9</v>
@@ -5502,9 +5553,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B229">
         <v>5.9</v>
@@ -5516,9 +5567,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B230">
         <v>5.9</v>
@@ -5530,9 +5581,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B231">
         <v>5.9</v>
@@ -5544,9 +5595,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B232">
         <v>5.9</v>
@@ -5558,9 +5609,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B233">
         <v>5.9</v>
@@ -5572,9 +5623,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B234">
         <v>5.9</v>
@@ -5586,9 +5637,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B235">
         <v>5.9</v>
@@ -5600,9 +5651,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B236">
         <v>5.9</v>
@@ -5614,9 +5665,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B237">
         <v>5.9</v>
@@ -5628,9 +5679,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B238">
         <v>5.9</v>
@@ -5642,9 +5693,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B239">
         <v>5.9</v>
@@ -5656,9 +5707,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B240">
         <v>5.9</v>
@@ -5670,9 +5721,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B241">
         <v>5.9</v>
@@ -5684,9 +5735,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B242">
         <v>5.9</v>
@@ -5698,9 +5749,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B243">
         <v>5.9</v>
@@ -5712,9 +5763,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B244">
         <v>5.9</v>
@@ -5726,9 +5777,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B245">
         <v>5.9</v>
@@ -5740,9 +5791,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B246">
         <v>5.9</v>
@@ -5754,9 +5805,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B247">
         <v>5.9</v>
@@ -5768,9 +5819,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B248">
         <v>5.9</v>
@@ -5782,9 +5833,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B249">
         <v>5.9</v>
@@ -5796,9 +5847,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B250">
         <v>5.9</v>
@@ -5810,9 +5861,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B251">
         <v>5.9</v>
@@ -5824,9 +5875,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B252">
         <v>5.9</v>
@@ -5838,9 +5889,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B253">
         <v>5.9</v>
@@ -5852,9 +5903,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B254">
         <v>5.9</v>
@@ -5866,9 +5917,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B255">
         <v>5.9</v>
@@ -5880,9 +5931,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B256">
         <v>5.9</v>
@@ -5894,9 +5945,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B257">
         <v>5.9</v>
@@ -5908,9 +5959,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B258">
         <v>5.9</v>
@@ -5922,9 +5973,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B259">
         <v>5.9</v>
@@ -5936,9 +5987,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B260">
         <v>5.9</v>
@@ -5950,9 +6001,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B261">
         <v>5.9</v>
@@ -5964,9 +6015,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B262">
         <v>6</v>
@@ -5978,9 +6029,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B263">
         <v>6</v>
@@ -5992,9 +6043,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B264">
         <v>6</v>
@@ -6006,9 +6057,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B265">
         <v>6</v>
@@ -6020,9 +6071,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B266">
         <v>6</v>
@@ -6034,9 +6085,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B267">
         <v>6</v>
@@ -6048,9 +6099,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B268">
         <v>6</v>
@@ -6062,9 +6113,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B269">
         <v>6</v>
@@ -6076,9 +6127,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B270">
         <v>6</v>
@@ -6090,9 +6141,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="271" spans="1:4">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B271">
         <v>6</v>
@@ -6104,9 +6155,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="272" spans="1:4">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B272">
         <v>6</v>
@@ -6118,9 +6169,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="273" spans="1:4">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B273">
         <v>6</v>
@@ -6132,9 +6183,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="274" spans="1:4">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B274">
         <v>6</v>
@@ -6146,9 +6197,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B275">
         <v>6</v>
@@ -6160,9 +6211,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="276" spans="1:4">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B276">
         <v>6</v>
@@ -6174,9 +6225,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B277">
         <v>6</v>
@@ -6188,9 +6239,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B278">
         <v>6</v>
@@ -6202,9 +6253,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B279">
         <v>6</v>
@@ -6216,9 +6267,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="280" spans="1:4">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B280">
         <v>6</v>
@@ -6230,9 +6281,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B281">
         <v>6</v>
@@ -6244,9 +6295,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="282" spans="1:4">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B282">
         <v>6</v>
@@ -6258,9 +6309,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B283">
         <v>6</v>
@@ -6272,9 +6323,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B284">
         <v>6</v>
@@ -6286,9 +6337,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B285">
         <v>6</v>
@@ -6300,9 +6351,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B286">
         <v>6</v>
@@ -6314,9 +6365,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B287">
         <v>6</v>
@@ -6328,9 +6379,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B288">
         <v>6</v>
@@ -6342,9 +6393,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B289">
         <v>6</v>
@@ -6356,9 +6407,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="290" spans="1:4">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B290">
         <v>6</v>
@@ -6370,9 +6421,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B291">
         <v>6</v>
@@ -6384,9 +6435,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B292">
         <v>6</v>
@@ -6398,9 +6449,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B293">
         <v>6</v>
@@ -6412,9 +6463,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="294" spans="1:4">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B294">
         <v>6</v>
@@ -6426,9 +6477,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="295" spans="1:4">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B295">
         <v>6</v>
@@ -6440,9 +6491,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="296" spans="1:4">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B296">
         <v>6</v>
@@ -6454,9 +6505,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B297">
         <v>6</v>
@@ -6468,9 +6519,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B298">
         <v>6</v>
@@ -6482,9 +6533,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B299">
         <v>6</v>
@@ -6496,9 +6547,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B300">
         <v>6</v>
@@ -6510,9 +6561,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B301">
         <v>6</v>
@@ -6524,9 +6575,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="302" spans="1:4">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B302">
         <v>6</v>
@@ -6538,9 +6589,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="303" spans="1:4">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B303">
         <v>6</v>
@@ -6552,9 +6603,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="304" spans="1:4">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B304">
         <v>6</v>
@@ -6566,9 +6617,9 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B305">
         <v>6</v>
@@ -6580,9 +6631,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B306">
         <v>6</v>
@@ -6594,9 +6645,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B307">
         <v>6</v>
@@ -6608,9 +6659,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B308">
         <v>6</v>
@@ -6622,9 +6673,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B309">
         <v>6</v>
@@ -6636,9 +6687,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B310">
         <v>6</v>
@@ -6650,9 +6701,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="311" spans="1:4">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B311">
         <v>6</v>
@@ -6664,9 +6715,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="312" spans="1:4">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B312">
         <v>6</v>
@@ -6678,9 +6729,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="313" spans="1:4">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B313">
         <v>6</v>
@@ -6692,9 +6743,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="314" spans="1:4">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B314">
         <v>6</v>
@@ -6706,9 +6757,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B315">
         <v>6</v>
@@ -6720,9 +6771,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="316" spans="1:4">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B316">
         <v>6</v>
@@ -6734,9 +6785,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="317" spans="1:4">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B317">
         <v>6</v>
@@ -6748,9 +6799,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B318">
         <v>6</v>
@@ -6762,9 +6813,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B319">
         <v>6</v>
@@ -6776,9 +6827,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B320">
         <v>6</v>
@@ -6790,9 +6841,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B321">
         <v>6</v>
@@ -6804,9 +6855,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B322">
         <v>6</v>
@@ -6818,9 +6869,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B323">
         <v>6</v>
@@ -6832,9 +6883,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B324">
         <v>6</v>
@@ -6846,9 +6897,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B325">
         <v>6</v>
@@ -6860,9 +6911,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B326">
         <v>6</v>
@@ -6874,9 +6925,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B327">
         <v>6</v>
@@ -6888,9 +6939,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="328" spans="1:4">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B328">
         <v>6.1</v>
@@ -6902,9 +6953,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B329">
         <v>6.1</v>
@@ -6916,9 +6967,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B330">
         <v>6.1</v>
@@ -6930,9 +6981,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B331">
         <v>6.1</v>
@@ -6944,9 +6995,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B332">
         <v>6.1</v>
@@ -6958,9 +7009,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B333">
         <v>6.1</v>
@@ -6972,9 +7023,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B334">
         <v>6.1</v>
@@ -6986,9 +7037,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B335">
         <v>6.1</v>
@@ -7000,9 +7051,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B336">
         <v>6.1</v>
@@ -7014,9 +7065,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="337" spans="1:4">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B337">
         <v>6.1</v>
@@ -7028,9 +7079,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="338" spans="1:4">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B338">
         <v>6.1</v>
@@ -7042,9 +7093,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B339">
         <v>6.1</v>
@@ -7056,9 +7107,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="340" spans="1:4">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B340">
         <v>6.1</v>
@@ -7070,9 +7121,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B341">
         <v>6.1</v>
@@ -7084,9 +7135,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="342" spans="1:4">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B342">
         <v>6.1</v>
@@ -7098,9 +7149,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="343" spans="1:4">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B343">
         <v>6.1</v>
@@ -7112,9 +7163,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="344" spans="1:4">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B344">
         <v>6.1</v>
@@ -7126,9 +7177,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="345" spans="1:4">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B345">
         <v>6.1</v>
@@ -7140,9 +7191,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="346" spans="1:4">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B346">
         <v>6.1</v>
@@ -7154,9 +7205,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="347" spans="1:4">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B347">
         <v>6.1</v>
@@ -7168,9 +7219,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="348" spans="1:4">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B348">
         <v>6.1</v>
@@ -7182,9 +7233,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="349" spans="1:4">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B349">
         <v>6.1</v>
@@ -7196,9 +7247,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="350" spans="1:4">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B350">
         <v>6.1</v>
@@ -7210,9 +7261,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="351" spans="1:4">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B351">
         <v>6.1</v>
@@ -7224,9 +7275,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="352" spans="1:4">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B352">
         <v>6.1</v>
@@ -7238,9 +7289,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="353" spans="1:4">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B353">
         <v>6.1</v>
@@ -7252,9 +7303,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="354" spans="1:4">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B354">
         <v>6.1</v>
@@ -7266,9 +7317,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="355" spans="1:4">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B355">
         <v>6.1</v>
@@ -7280,9 +7331,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="356" spans="1:4">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B356">
         <v>6.1</v>
@@ -7294,9 +7345,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="357" spans="1:4">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B357">
         <v>6.1</v>
@@ -7308,9 +7359,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="358" spans="1:4">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B358">
         <v>6.1</v>
@@ -7322,9 +7373,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="359" spans="1:4">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B359">
         <v>6.1</v>
@@ -7336,9 +7387,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="360" spans="1:4">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B360">
         <v>6.1</v>
@@ -7350,9 +7401,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="361" spans="1:4">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B361">
         <v>6.1</v>
@@ -7364,9 +7415,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="362" spans="1:4">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B362">
         <v>6.1</v>
@@ -7378,9 +7429,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="363" spans="1:4">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B363">
         <v>6.1</v>
@@ -7392,9 +7443,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="364" spans="1:4">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B364">
         <v>6.1</v>
@@ -7406,9 +7457,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="365" spans="1:4">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B365">
         <v>6.1</v>
@@ -7420,9 +7471,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="366" spans="1:4">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B366">
         <v>6.1</v>
@@ -7434,9 +7485,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="367" spans="1:4">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B367">
         <v>6.1</v>
@@ -7448,9 +7499,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="368" spans="1:4">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B368">
         <v>6.1</v>
@@ -7462,9 +7513,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="369" spans="1:4">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B369">
         <v>6.1</v>
@@ -7476,9 +7527,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="370" spans="1:4">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B370">
         <v>6.1</v>
@@ -7490,9 +7541,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="371" spans="1:4">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B371">
         <v>6.1</v>
@@ -7504,9 +7555,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="372" spans="1:4">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B372">
         <v>6.1</v>
@@ -7518,9 +7569,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="373" spans="1:4">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B373">
         <v>6.1</v>
@@ -7532,9 +7583,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="374" spans="1:4">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B374">
         <v>6.1</v>
@@ -7546,9 +7597,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="375" spans="1:4">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B375">
         <v>6.1</v>
@@ -7560,9 +7611,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="376" spans="1:4">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B376">
         <v>6.1</v>
@@ -7574,9 +7625,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="377" spans="1:4">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B377">
         <v>6.1</v>
@@ -7588,9 +7639,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="378" spans="1:4">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B378">
         <v>6.1</v>
@@ -7602,9 +7653,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="379" spans="1:4">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B379">
         <v>6.1</v>
@@ -7616,9 +7667,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="380" spans="1:4">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B380">
         <v>6.1</v>
@@ -7630,9 +7681,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="381" spans="1:4">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B381">
         <v>6.1</v>
@@ -7644,9 +7695,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="382" spans="1:4">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B382">
         <v>6.1</v>
@@ -7658,9 +7709,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="383" spans="1:4">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B383">
         <v>6.1</v>
@@ -7672,9 +7723,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="384" spans="1:4">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B384">
         <v>6.1</v>
@@ -7686,9 +7737,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="385" spans="1:4">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B385">
         <v>6.1</v>
@@ -7700,9 +7751,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="386" spans="1:4">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B386">
         <v>6.1</v>
@@ -7714,9 +7765,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="387" spans="1:4">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B387">
         <v>6.1</v>
@@ -7728,9 +7779,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="388" spans="1:4">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B388">
         <v>6.1</v>
@@ -7742,9 +7793,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="389" spans="1:4">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B389">
         <v>6.1</v>
@@ -7756,9 +7807,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="390" spans="1:4">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B390">
         <v>6.1</v>
@@ -7770,9 +7821,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="391" spans="1:4">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B391">
         <v>6.1</v>
@@ -7784,9 +7835,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="392" spans="1:4">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B392">
         <v>6.1</v>
@@ -7798,9 +7849,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="393" spans="1:4">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B393">
         <v>6.1</v>
@@ -7812,9 +7863,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="394" spans="1:4">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B394">
         <v>6.1</v>
@@ -7826,9 +7877,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="395" spans="1:4">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B395">
         <v>6.1</v>
@@ -7840,9 +7891,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="396" spans="1:4">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B396">
         <v>6.1</v>
@@ -7854,9 +7905,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="397" spans="1:4">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B397">
         <v>6.1</v>
@@ -7868,9 +7919,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="398" spans="1:4">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B398">
         <v>6.1</v>
@@ -7882,9 +7933,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="399" spans="1:4">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B399">
         <v>6.1</v>
@@ -7896,9 +7947,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="400" spans="1:4">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B400">
         <v>6.1</v>
@@ -7910,9 +7961,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="401" spans="1:4">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B401">
         <v>6.1</v>
@@ -7924,9 +7975,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="402" spans="1:4">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B402">
         <v>6.1</v>
@@ -7938,9 +7989,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="403" spans="1:4">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B403">
         <v>6.1</v>
@@ -7952,9 +8003,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="404" spans="1:4">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B404">
         <v>6.1</v>
@@ -7966,9 +8017,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="405" spans="1:4">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B405">
         <v>6.1</v>
@@ -7980,9 +8031,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="406" spans="1:4">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B406">
         <v>6.1</v>
@@ -7994,9 +8045,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="407" spans="1:4">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B407">
         <v>6.1</v>
@@ -8008,9 +8059,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="408" spans="1:4">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B408">
         <v>6.1</v>
@@ -8022,9 +8073,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="409" spans="1:4">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B409">
         <v>6.1</v>
@@ -8036,9 +8087,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="410" spans="1:4">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B410">
         <v>6.1</v>
@@ -8050,9 +8101,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="411" spans="1:4">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B411">
         <v>6.1</v>
@@ -8064,9 +8115,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="412" spans="1:4">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B412">
         <v>6.1</v>
@@ -8078,9 +8129,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="413" spans="1:4">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B413">
         <v>6.1</v>
@@ -8092,9 +8143,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="414" spans="1:4">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B414">
         <v>6.1</v>
@@ -8106,9 +8157,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="415" spans="1:4">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B415">
         <v>6.1</v>
@@ -8120,9 +8171,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="416" spans="1:4">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B416">
         <v>6.1</v>
@@ -8134,9 +8185,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="417" spans="1:4">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B417">
         <v>6.1</v>
@@ -8148,9 +8199,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="418" spans="1:4">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B418">
         <v>6.1</v>
@@ -8162,9 +8213,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="419" spans="1:4">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B419">
         <v>6.1</v>
@@ -8176,9 +8227,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="420" spans="1:4">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B420">
         <v>6.1</v>
@@ -8190,9 +8241,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="421" spans="1:4">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B421">
         <v>6.1</v>
@@ -8204,9 +8255,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="422" spans="1:4">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B422">
         <v>6.1</v>
@@ -8218,9 +8269,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="423" spans="1:4">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B423">
         <v>6.1</v>
@@ -8232,9 +8283,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="424" spans="1:4">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B424">
         <v>6.1</v>
@@ -8246,9 +8297,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="425" spans="1:4">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B425">
         <v>6.1</v>
@@ -8260,9 +8311,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="426" spans="1:4">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B426">
         <v>6.1</v>
@@ -8274,9 +8325,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="427" spans="1:4">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B427">
         <v>6.1</v>
@@ -8288,9 +8339,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="428" spans="1:4">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B428">
         <v>6.1</v>
@@ -8302,9 +8353,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="429" spans="1:4">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B429">
         <v>6.1</v>
@@ -8316,9 +8367,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="430" spans="1:4">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B430">
         <v>6.1</v>
@@ -8330,9 +8381,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="431" spans="1:4">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B431">
         <v>6.1</v>
@@ -8344,9 +8395,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="432" spans="1:4">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B432">
         <v>6.1</v>
@@ -8358,9 +8409,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="433" spans="1:4">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B433">
         <v>6.1</v>
@@ -8372,9 +8423,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="434" spans="1:4">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B434">
         <v>6.1</v>
@@ -8386,9 +8437,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="435" spans="1:4">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B435">
         <v>6.1</v>
@@ -8400,9 +8451,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="436" spans="1:4">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B436">
         <v>6.1</v>
@@ -8414,9 +8465,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="437" spans="1:4">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B437">
         <v>6.1</v>
@@ -8428,9 +8479,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="438" spans="1:4">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B438">
         <v>6.1</v>
@@ -8442,9 +8493,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="439" spans="1:4">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B439">
         <v>6.1</v>
@@ -8456,9 +8507,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="440" spans="1:4">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B440">
         <v>6</v>
@@ -8470,9 +8521,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="441" spans="1:4">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B441">
         <v>6</v>
@@ -8484,9 +8535,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="442" spans="1:4">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="B442">
         <v>6</v>
@@ -8498,9 +8549,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="443" spans="1:4">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B443">
         <v>6</v>
@@ -8512,9 +8563,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="444" spans="1:4">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B444">
         <v>6</v>
@@ -8526,9 +8577,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="445" spans="1:4">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B445">
         <v>6</v>
@@ -8540,9 +8591,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="446" spans="1:4">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B446">
         <v>6</v>
@@ -8554,9 +8605,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="447" spans="1:4">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B447">
         <v>6</v>
@@ -8568,9 +8619,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="448" spans="1:4">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B448">
         <v>6</v>
@@ -8582,9 +8633,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="449" spans="1:4">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B449">
         <v>6</v>
@@ -8596,9 +8647,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="450" spans="1:4">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B450">
         <v>6</v>
@@ -8610,9 +8661,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="451" spans="1:4">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B451">
         <v>6</v>
@@ -8624,9 +8675,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="452" spans="1:4">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B452">
         <v>6</v>
@@ -8638,9 +8689,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="453" spans="1:4">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B453">
         <v>6</v>
@@ -8652,9 +8703,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="454" spans="1:4">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B454">
         <v>6</v>
@@ -8666,9 +8717,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="455" spans="1:4">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B455">
         <v>6</v>
@@ -8680,9 +8731,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="456" spans="1:4">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B456">
         <v>6</v>
@@ -8694,9 +8745,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="457" spans="1:4">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B457">
         <v>6</v>
@@ -8708,9 +8759,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="458" spans="1:4">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B458">
         <v>6</v>
@@ -8722,9 +8773,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="459" spans="1:4">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B459">
         <v>6</v>
@@ -8736,9 +8787,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="460" spans="1:4">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B460">
         <v>6</v>
@@ -8750,9 +8801,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="461" spans="1:4">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B461">
         <v>6</v>
@@ -8764,9 +8815,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="462" spans="1:4">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B462">
         <v>6</v>
@@ -8778,9 +8829,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="463" spans="1:4">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B463">
         <v>6</v>
@@ -8792,9 +8843,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="464" spans="1:4">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B464">
         <v>6</v>
@@ -8806,9 +8857,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="465" spans="1:4">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B465">
         <v>6</v>
@@ -8820,9 +8871,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="466" spans="1:4">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B466">
         <v>6</v>
@@ -8834,9 +8885,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="467" spans="1:4">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B467">
         <v>6</v>
@@ -8848,9 +8899,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="468" spans="1:4">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B468">
         <v>6</v>
@@ -8862,9 +8913,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="469" spans="1:4">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B469">
         <v>6</v>
@@ -8876,9 +8927,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="470" spans="1:4">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B470">
         <v>6</v>
@@ -8890,9 +8941,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="471" spans="1:4">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B471">
         <v>6</v>
@@ -8904,9 +8955,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="472" spans="1:4">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B472">
         <v>6</v>
@@ -8918,9 +8969,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="473" spans="1:4">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B473">
         <v>6</v>
@@ -8932,9 +8983,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="474" spans="1:4">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B474">
         <v>6</v>
@@ -8946,9 +8997,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="475" spans="1:4">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B475">
         <v>6</v>
@@ -8960,9 +9011,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="476" spans="1:4">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B476">
         <v>6</v>
@@ -8974,9 +9025,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="477" spans="1:4">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B477">
         <v>6</v>
@@ -8988,9 +9039,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="478" spans="1:4">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B478">
         <v>6</v>
@@ -9002,9 +9053,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="479" spans="1:4">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B479">
         <v>6</v>
@@ -9016,9 +9067,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="480" spans="1:4">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B480">
         <v>6</v>
@@ -9030,9 +9081,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="481" spans="1:4">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B481">
         <v>6</v>
@@ -9044,9 +9095,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="482" spans="1:4">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B482">
         <v>6</v>
@@ -9058,9 +9109,9 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="483" spans="1:4">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B483">
         <v>6</v>
@@ -9072,9 +9123,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="484" spans="1:4">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B484">
         <v>6</v>
@@ -9086,9 +9137,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="485" spans="1:4">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B485">
         <v>6</v>
@@ -9100,9 +9151,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="486" spans="1:4">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B486">
         <v>6</v>
@@ -9114,9 +9165,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="487" spans="1:4">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B487">
         <v>6</v>
@@ -9128,9 +9179,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="488" spans="1:4">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B488">
         <v>6</v>
@@ -9142,9 +9193,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="489" spans="1:4">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B489">
         <v>6</v>
@@ -9156,9 +9207,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="490" spans="1:4">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B490">
         <v>6</v>
@@ -9170,9 +9221,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="491" spans="1:4">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B491">
         <v>6</v>
@@ -9184,9 +9235,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="492" spans="1:4">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B492">
         <v>6</v>
@@ -9198,9 +9249,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="493" spans="1:4">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B493">
         <v>6</v>
@@ -9212,9 +9263,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="494" spans="1:4">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B494">
         <v>6</v>
@@ -9226,9 +9277,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="495" spans="1:4">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B495">
         <v>6</v>
@@ -9240,9 +9291,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="496" spans="1:4">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B496">
         <v>6</v>
@@ -9254,9 +9305,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="497" spans="1:4">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B497">
         <v>6</v>
@@ -9268,9 +9319,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="498" spans="1:4">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B498">
         <v>6</v>
@@ -9282,9 +9333,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="499" spans="1:4">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B499">
         <v>6</v>
@@ -9296,9 +9347,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="500" spans="1:4">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B500">
         <v>6</v>
@@ -9310,9 +9361,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="501" spans="1:4">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B501">
         <v>6</v>
@@ -9324,9 +9375,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="502" spans="1:4">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B502">
         <v>6</v>
@@ -9338,9 +9389,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="503" spans="1:4">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B503">
         <v>6</v>
@@ -9352,9 +9403,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="504" spans="1:4">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B504">
         <v>6</v>
@@ -9366,9 +9417,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="505" spans="1:4">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B505">
         <v>6</v>
@@ -9380,9 +9431,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="506" spans="1:4">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B506">
         <v>6</v>
@@ -9394,9 +9445,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="507" spans="1:4">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B507">
         <v>6</v>
@@ -9408,9 +9459,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="508" spans="1:4">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B508">
         <v>6</v>
@@ -9422,9 +9473,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="509" spans="1:4">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B509">
         <v>6</v>
@@ -9436,9 +9487,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="510" spans="1:4">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B510">
         <v>6</v>
@@ -9450,9 +9501,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="511" spans="1:4">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B511">
         <v>6</v>
@@ -9464,9 +9515,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="512" spans="1:4">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B512">
         <v>6</v>
@@ -9478,9 +9529,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="513" spans="1:4">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B513">
         <v>6</v>
@@ -9492,9 +9543,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="514" spans="1:4">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B514">
         <v>6</v>
@@ -9506,9 +9557,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="515" spans="1:4">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B515">
         <v>6</v>
@@ -9520,9 +9571,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="516" spans="1:4">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B516">
         <v>6</v>
@@ -9534,9 +9585,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="517" spans="1:4">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B517">
         <v>6</v>
@@ -9548,9 +9599,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="518" spans="1:4">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B518">
         <v>6</v>
@@ -9562,9 +9613,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="519" spans="1:4">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B519">
         <v>6</v>
@@ -9576,9 +9627,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="520" spans="1:4">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B520">
         <v>6</v>
@@ -9590,9 +9641,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="521" spans="1:4">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B521">
         <v>6</v>
@@ -9604,9 +9655,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="522" spans="1:4">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B522">
         <v>6</v>
@@ -9618,9 +9669,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="523" spans="1:4">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B523">
         <v>6</v>
@@ -9632,9 +9683,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="524" spans="1:4">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B524">
         <v>6</v>
@@ -9646,9 +9697,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="525" spans="1:4">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B525">
         <v>6</v>
@@ -9660,9 +9711,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="526" spans="1:4">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B526">
         <v>6</v>
@@ -9674,9 +9725,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="527" spans="1:4">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B527">
         <v>6</v>
@@ -9688,9 +9739,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="528" spans="1:4">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B528">
         <v>6</v>
@@ -9702,9 +9753,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="529" spans="1:4">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B529">
         <v>6</v>
@@ -9716,9 +9767,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="530" spans="1:4">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B530">
         <v>6</v>
@@ -9730,9 +9781,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="531" spans="1:4">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B531">
         <v>6</v>
@@ -9744,9 +9795,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="532" spans="1:4">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B532">
         <v>6</v>
@@ -9758,9 +9809,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="533" spans="1:4">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B533">
         <v>6</v>
@@ -9772,9 +9823,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="534" spans="1:4">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B534">
         <v>6</v>
@@ -9786,9 +9837,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="535" spans="1:4">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B535">
         <v>6</v>
@@ -9800,9 +9851,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="536" spans="1:4">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B536">
         <v>6</v>
@@ -9814,9 +9865,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="537" spans="1:4">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B537">
         <v>6</v>
@@ -9828,9 +9879,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="538" spans="1:4">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B538">
         <v>6</v>
@@ -9842,9 +9893,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="539" spans="1:4">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B539">
         <v>6</v>
@@ -9856,9 +9907,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="540" spans="1:4">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B540">
         <v>6</v>
@@ -9870,9 +9921,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="541" spans="1:4">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B541">
         <v>6</v>
@@ -9884,9 +9935,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="542" spans="1:4">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B542">
         <v>6</v>
@@ -9898,9 +9949,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="543" spans="1:4">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B543">
         <v>6</v>
@@ -9912,9 +9963,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="544" spans="1:4">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B544">
         <v>6</v>
@@ -9926,9 +9977,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="545" spans="1:4">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B545">
         <v>6</v>
@@ -9940,9 +9991,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="546" spans="1:4">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B546">
         <v>6</v>
@@ -9954,9 +10005,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="547" spans="1:4">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B547">
         <v>6</v>
@@ -9968,9 +10019,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="548" spans="1:4">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B548">
         <v>6</v>
@@ -9982,9 +10033,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="549" spans="1:4">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B549">
         <v>6.1</v>
@@ -9996,9 +10047,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="550" spans="1:4">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B550">
         <v>6.1</v>
@@ -10010,9 +10061,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="551" spans="1:4">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B551">
         <v>6.1</v>
@@ -10024,9 +10075,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="552" spans="1:4">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B552">
         <v>6.1</v>
@@ -10038,9 +10089,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="553" spans="1:4">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B553">
         <v>6.1</v>
@@ -10052,9 +10103,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="554" spans="1:4">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B554">
         <v>6.1</v>
@@ -10066,9 +10117,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="555" spans="1:4">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B555">
         <v>6.1</v>
@@ -10080,9 +10131,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="556" spans="1:4">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B556">
         <v>6.1</v>
@@ -10094,9 +10145,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="557" spans="1:4">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B557">
         <v>6.1</v>
@@ -10108,9 +10159,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="558" spans="1:4">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B558">
         <v>6.1</v>
@@ -10122,9 +10173,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="559" spans="1:4">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B559">
         <v>6.1</v>
@@ -10136,9 +10187,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="560" spans="1:4">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B560">
         <v>6.1</v>
@@ -10150,9 +10201,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="561" spans="1:4">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B561">
         <v>6.1</v>
@@ -10164,9 +10215,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="562" spans="1:4">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B562">
         <v>6.1</v>
@@ -10178,9 +10229,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="563" spans="1:4">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B563">
         <v>6.1</v>
@@ -10192,9 +10243,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="564" spans="1:4">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B564">
         <v>6.1</v>
@@ -10206,9 +10257,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="565" spans="1:4">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B565">
         <v>6.1</v>
@@ -10220,9 +10271,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="566" spans="1:4">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B566">
         <v>6.1</v>
@@ -10234,9 +10285,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="567" spans="1:4">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B567">
         <v>6.1</v>
@@ -10248,9 +10299,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="568" spans="1:4">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B568">
         <v>6.1</v>
@@ -10262,9 +10313,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="569" spans="1:4">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B569">
         <v>6.1</v>
@@ -10276,9 +10327,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="570" spans="1:4">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B570">
         <v>6.1</v>
@@ -10290,9 +10341,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="571" spans="1:4">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B571">
         <v>6.1</v>
@@ -10304,9 +10355,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="572" spans="1:4">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B572">
         <v>6.1</v>
@@ -10318,9 +10369,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="573" spans="1:4">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B573">
         <v>6.1</v>
@@ -10332,9 +10383,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="574" spans="1:4">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B574">
         <v>6.1</v>
@@ -10346,9 +10397,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="575" spans="1:4">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B575">
         <v>6.1</v>
@@ -10360,9 +10411,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="576" spans="1:4">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B576">
         <v>6.1</v>
@@ -10374,9 +10425,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="577" spans="1:4">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B577">
         <v>6.1</v>
@@ -10388,9 +10439,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="578" spans="1:4">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B578">
         <v>6.1</v>
@@ -10402,9 +10453,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="579" spans="1:4">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B579">
         <v>6.1</v>
@@ -10416,9 +10467,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="580" spans="1:4">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B580">
         <v>6.1</v>
@@ -10430,9 +10481,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="581" spans="1:4">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B581">
         <v>6.1</v>
@@ -10444,9 +10495,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="582" spans="1:4">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B582">
         <v>6.1</v>
@@ -10458,9 +10509,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="583" spans="1:4">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B583">
         <v>6.1</v>
@@ -10472,9 +10523,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="584" spans="1:4">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B584">
         <v>6.1</v>
@@ -10486,9 +10537,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="585" spans="1:4">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B585">
         <v>6.1</v>
@@ -10500,9 +10551,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="586" spans="1:4">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B586">
         <v>6.1</v>
@@ -10514,9 +10565,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="587" spans="1:4">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B587">
         <v>6.1</v>
@@ -10528,9 +10579,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="588" spans="1:4">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B588">
         <v>6.1</v>
@@ -10542,9 +10593,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="589" spans="1:4">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B589">
         <v>6.1</v>
@@ -10556,9 +10607,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="590" spans="1:4">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B590">
         <v>6.1</v>
@@ -10570,9 +10621,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="591" spans="1:4">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B591">
         <v>6.1</v>
@@ -10584,9 +10635,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="592" spans="1:4">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B592">
         <v>6.1</v>
@@ -10598,9 +10649,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="593" spans="1:4">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B593">
         <v>6</v>
@@ -10612,9 +10663,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="594" spans="1:4">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B594">
         <v>6</v>
@@ -10626,9 +10677,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="595" spans="1:4">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B595">
         <v>6</v>
@@ -10640,9 +10691,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="596" spans="1:4">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B596">
         <v>6</v>
@@ -10654,9 +10705,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="597" spans="1:4">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B597">
         <v>6</v>
@@ -10668,9 +10719,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="598" spans="1:4">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B598">
         <v>6</v>
@@ -10682,9 +10733,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="599" spans="1:4">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B599">
         <v>6</v>
@@ -10696,9 +10747,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="600" spans="1:4">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B600">
         <v>6</v>
@@ -10710,9 +10761,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="601" spans="1:4">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B601">
         <v>6</v>
@@ -10724,9 +10775,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="602" spans="1:4">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B602">
         <v>6</v>
@@ -10738,9 +10789,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="603" spans="1:4">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B603">
         <v>6</v>
@@ -10752,9 +10803,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="604" spans="1:4">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B604">
         <v>6</v>
@@ -10766,9 +10817,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="605" spans="1:4">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B605">
         <v>6</v>
@@ -10780,9 +10831,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="606" spans="1:4">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B606">
         <v>6</v>
@@ -10794,9 +10845,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="607" spans="1:4">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B607">
         <v>6</v>
@@ -10808,9 +10859,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="608" spans="1:4">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="B608">
         <v>6</v>
@@ -10822,9 +10873,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="609" spans="1:4">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B609">
         <v>6</v>
@@ -10836,9 +10887,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="610" spans="1:4">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="B610">
         <v>6</v>
@@ -10850,9 +10901,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="611" spans="1:4">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B611">
         <v>6</v>
@@ -10864,9 +10915,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="612" spans="1:4">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B612">
         <v>6</v>
@@ -10878,9 +10929,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="613" spans="1:4">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B613">
         <v>6</v>
@@ -10892,9 +10943,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="614" spans="1:4">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B614">
         <v>6</v>
@@ -10906,9 +10957,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="615" spans="1:4">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B615">
         <v>6</v>
@@ -10920,9 +10971,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="616" spans="1:4">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B616">
         <v>6</v>
@@ -10934,9 +10985,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="617" spans="1:4">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="B617">
         <v>6</v>
@@ -10948,9 +10999,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="618" spans="1:4">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B618">
         <v>6</v>
@@ -10962,9 +11013,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="619" spans="1:4">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B619">
         <v>6</v>
@@ -10976,9 +11027,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="620" spans="1:4">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B620">
         <v>6</v>
@@ -10990,9 +11041,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="621" spans="1:4">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B621">
         <v>6</v>
@@ -11004,9 +11055,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="622" spans="1:4">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B622">
         <v>6</v>
@@ -11018,9 +11069,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="623" spans="1:4">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B623">
         <v>6</v>
@@ -11032,9 +11083,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="624" spans="1:4">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B624">
         <v>6</v>
@@ -11046,9 +11097,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="625" spans="1:4">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B625">
         <v>6</v>
@@ -11060,9 +11111,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="626" spans="1:4">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B626">
         <v>6</v>
@@ -11074,9 +11125,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="627" spans="1:4">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B627">
         <v>6</v>
@@ -11088,9 +11139,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="628" spans="1:4">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B628">
         <v>6</v>
@@ -11102,9 +11153,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="629" spans="1:4">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B629">
         <v>6</v>
@@ -11116,9 +11167,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="630" spans="1:4">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B630">
         <v>6</v>
@@ -11130,9 +11181,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="631" spans="1:4">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B631">
         <v>6</v>
@@ -11144,9 +11195,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="632" spans="1:4">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B632">
         <v>6</v>
@@ -11158,9 +11209,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="633" spans="1:4">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B633">
         <v>6</v>
@@ -11172,9 +11223,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="634" spans="1:4">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B634">
         <v>6</v>
@@ -11186,9 +11237,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="635" spans="1:4">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B635">
         <v>6</v>
@@ -11200,9 +11251,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="636" spans="1:4">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="B636">
         <v>6</v>
@@ -11214,9 +11265,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="637" spans="1:4">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B637">
         <v>6</v>
@@ -11228,9 +11279,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="638" spans="1:4">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B638">
         <v>6</v>
@@ -11242,9 +11293,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="639" spans="1:4">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B639">
         <v>6</v>
@@ -11256,9 +11307,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="640" spans="1:4">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B640">
         <v>6</v>
@@ -11270,9 +11321,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="641" spans="1:4">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B641">
         <v>6</v>
@@ -11284,9 +11335,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="642" spans="1:4">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B642">
         <v>6</v>
@@ -11298,9 +11349,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="643" spans="1:4">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B643">
         <v>6</v>
@@ -11312,9 +11363,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="644" spans="1:4">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B644">
         <v>6</v>
@@ -11326,9 +11377,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="645" spans="1:4">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B645">
         <v>6</v>
@@ -11340,9 +11391,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="646" spans="1:4">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B646">
         <v>6</v>
@@ -11354,9 +11405,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="647" spans="1:4">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B647">
         <v>6</v>
@@ -11368,9 +11419,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="648" spans="1:4">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="B648">
         <v>6</v>
@@ -11382,9 +11433,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="649" spans="1:4">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B649">
         <v>6</v>
@@ -11396,9 +11447,9 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="650" spans="1:4">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="B650">
         <v>6</v>
@@ -11410,7 +11461,37 @@
         <v>11.8</v>
       </c>
     </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>655</v>
+      </c>
+      <c r="B651">
+        <v>6</v>
+      </c>
+      <c r="C651">
+        <v>2.7</v>
+      </c>
+      <c r="D651">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>656</v>
+      </c>
+      <c r="B652">
+        <v>6</v>
+      </c>
+      <c r="C652">
+        <v>2.7</v>
+      </c>
+      <c r="D652">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>